--- a/rice_data/R8年産ゆめぴりか定点観測集計表.xlsx
+++ b/rice_data/R8年産ゆめぴりか定点観測集計表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00093045\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9236035B-5600-4DE2-B088-2A8954501F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47E3BFD1-51E3-4816-BA4E-06043B66F92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="506">
   <si>
     <t>令和8年度「ゆめぴりか」食味関連成分含有率定点観測分析</t>
     <rPh sb="0" eb="2">
@@ -1370,6 +1370,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>密苗</t>
+  </si>
+  <si>
     <t>北いぶき</t>
   </si>
   <si>
@@ -1479,7 +1482,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>成苗ポット</t>
+    <t>成苗</t>
     <rPh sb="0" eb="2">
       <t>セイビョウ</t>
     </rPh>
@@ -1772,13 +1775,6 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>ホクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>成苗</t>
-    <rPh sb="0" eb="2">
-      <t>セイビョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2196,6 +2192,13 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ヒロシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成苗ポット</t>
+    <rPh sb="0" eb="2">
+      <t>セイビョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6668,7 +6671,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="888">
+  <cellXfs count="891">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9066,6 +9069,36 @@
     <xf numFmtId="176" fontId="38" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="37" fillId="8" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="4" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="40" fontId="4" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="40" fontId="4" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9108,9 +9141,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9135,22 +9165,10 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="40" fontId="4" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="40" fontId="4" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="40" fontId="4" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9168,12 +9186,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="76" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="2" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9210,6 +9222,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="2" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9223,30 +9259,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="2" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9651,21 +9663,21 @@
   <dimension ref="A1:P57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.375" style="523" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="523" customWidth="1"/>
     <col min="2" max="2" width="9" style="523"/>
-    <col min="3" max="4" width="13.375" style="523" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="523" customWidth="1"/>
-    <col min="6" max="6" width="36.625" style="523" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="523" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="523" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="523" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="523" customWidth="1"/>
+    <col min="6" max="6" width="36.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="523" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.375" style="28" customWidth="1"/>
+    <col min="13" max="13" width="16.5" style="28" customWidth="1"/>
     <col min="14" max="14" width="15.875" style="523" customWidth="1"/>
     <col min="15" max="15" width="9" style="523"/>
-    <col min="16" max="16" width="14.625" style="776" customWidth="1"/>
+    <col min="16" max="16" width="14.5" style="776" customWidth="1"/>
     <col min="17" max="16384" width="9" style="523"/>
   </cols>
   <sheetData>
@@ -9687,19 +9699,19 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="35.85" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="799" t="s">
+      <c r="A3" s="809" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="800"/>
-      <c r="C3" s="800"/>
-      <c r="D3" s="800"/>
-      <c r="E3" s="800"/>
-      <c r="F3" s="800"/>
-      <c r="G3" s="800"/>
-      <c r="H3" s="800"/>
-      <c r="I3" s="800"/>
-      <c r="J3" s="800"/>
-      <c r="K3" s="801"/>
+      <c r="B3" s="810"/>
+      <c r="C3" s="810"/>
+      <c r="D3" s="810"/>
+      <c r="E3" s="810"/>
+      <c r="F3" s="810"/>
+      <c r="G3" s="810"/>
+      <c r="H3" s="810"/>
+      <c r="I3" s="810"/>
+      <c r="J3" s="810"/>
+      <c r="K3" s="811"/>
       <c r="L3" s="769" t="s">
         <v>3</v>
       </c>
@@ -9714,18 +9726,18 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A4" s="802" t="s">
+      <c r="A4" s="812" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="802"/>
-      <c r="C4" s="802"/>
-      <c r="D4" s="802"/>
-      <c r="E4" s="802"/>
-      <c r="F4" s="802"/>
-      <c r="G4" s="803" t="s">
+      <c r="B4" s="812"/>
+      <c r="C4" s="812"/>
+      <c r="D4" s="812"/>
+      <c r="E4" s="812"/>
+      <c r="F4" s="812"/>
+      <c r="G4" s="813" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="803" t="s">
+      <c r="H4" s="813" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="622" t="s">
@@ -9740,88 +9752,88 @@
       <c r="L4" s="742" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="806" t="s">
+      <c r="M4" s="816" t="s">
         <v>14</v>
       </c>
       <c r="N4" s="699"/>
-      <c r="P4" s="822" t="s">
+      <c r="P4" s="802" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="813" t="s">
+      <c r="A5" s="805" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="825" t="s">
+      <c r="B5" s="806" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="813" t="s">
+      <c r="C5" s="805" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="813" t="s">
+      <c r="D5" s="805" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="810" t="s">
+      <c r="E5" s="820" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="813" t="s">
+      <c r="F5" s="805" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="804"/>
-      <c r="H5" s="804"/>
+      <c r="G5" s="814"/>
+      <c r="H5" s="814"/>
       <c r="I5" s="623"/>
       <c r="J5" s="671"/>
       <c r="K5" s="671" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="743"/>
-      <c r="M5" s="807"/>
+      <c r="M5" s="817"/>
       <c r="N5" s="700"/>
-      <c r="P5" s="823"/>
+      <c r="P5" s="803"/>
     </row>
     <row r="6" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="813"/>
-      <c r="B6" s="825"/>
-      <c r="C6" s="813"/>
-      <c r="D6" s="813"/>
-      <c r="E6" s="811"/>
-      <c r="F6" s="813"/>
-      <c r="G6" s="804"/>
-      <c r="H6" s="804"/>
-      <c r="I6" s="814" t="s">
+      <c r="A6" s="805"/>
+      <c r="B6" s="806"/>
+      <c r="C6" s="805"/>
+      <c r="D6" s="805"/>
+      <c r="E6" s="821"/>
+      <c r="F6" s="805"/>
+      <c r="G6" s="814"/>
+      <c r="H6" s="814"/>
+      <c r="I6" s="823" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="816" t="s">
+      <c r="J6" s="825" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="818" t="s">
+      <c r="K6" s="827" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="820" t="s">
+      <c r="L6" s="829" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="808" t="s">
+      <c r="M6" s="818" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="826"/>
-      <c r="P6" s="823"/>
+      <c r="N6" s="807"/>
+      <c r="P6" s="803"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A7" s="813"/>
-      <c r="B7" s="825"/>
-      <c r="C7" s="813"/>
-      <c r="D7" s="813"/>
-      <c r="E7" s="812"/>
-      <c r="F7" s="813"/>
-      <c r="G7" s="805"/>
-      <c r="H7" s="805"/>
-      <c r="I7" s="815"/>
-      <c r="J7" s="817"/>
-      <c r="K7" s="819"/>
-      <c r="L7" s="821"/>
-      <c r="M7" s="809"/>
-      <c r="N7" s="827"/>
-      <c r="P7" s="824"/>
+      <c r="A7" s="805"/>
+      <c r="B7" s="806"/>
+      <c r="C7" s="805"/>
+      <c r="D7" s="805"/>
+      <c r="E7" s="822"/>
+      <c r="F7" s="805"/>
+      <c r="G7" s="815"/>
+      <c r="H7" s="815"/>
+      <c r="I7" s="824"/>
+      <c r="J7" s="826"/>
+      <c r="K7" s="828"/>
+      <c r="L7" s="830"/>
+      <c r="M7" s="819"/>
+      <c r="N7" s="808"/>
+      <c r="P7" s="804"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="507">
@@ -9857,7 +9869,9 @@
       <c r="K8" s="672" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="744"/>
+      <c r="L8" s="744">
+        <v>46228</v>
+      </c>
       <c r="M8" s="757"/>
       <c r="N8" s="701"/>
       <c r="P8" s="778"/>
@@ -9896,7 +9910,9 @@
       <c r="K9" s="791" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="745"/>
+      <c r="L9" s="745">
+        <v>46228</v>
+      </c>
       <c r="M9" s="758"/>
       <c r="N9" s="711"/>
       <c r="P9" s="779"/>
@@ -9933,7 +9949,9 @@
       <c r="K10" s="675" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="746"/>
+      <c r="L10" s="801">
+        <v>46235</v>
+      </c>
       <c r="M10" s="759"/>
       <c r="N10" s="703"/>
       <c r="P10" s="780"/>
@@ -9972,7 +9990,9 @@
       <c r="K11" s="696" t="s">
         <v>46</v>
       </c>
-      <c r="L11" s="747"/>
+      <c r="L11" s="747">
+        <v>46228</v>
+      </c>
       <c r="M11" s="760"/>
       <c r="N11" s="702"/>
       <c r="P11" s="779"/>
@@ -10011,7 +10031,9 @@
       <c r="K12" s="497" t="s">
         <v>51</v>
       </c>
-      <c r="L12" s="747"/>
+      <c r="L12" s="747">
+        <v>46230</v>
+      </c>
       <c r="M12" s="761"/>
       <c r="N12" s="702"/>
       <c r="P12" s="779"/>
@@ -10048,7 +10070,9 @@
       <c r="K13" s="680" t="s">
         <v>51</v>
       </c>
-      <c r="L13" s="748"/>
+      <c r="L13" s="748">
+        <v>46218</v>
+      </c>
       <c r="M13" s="762"/>
       <c r="N13" s="703"/>
       <c r="P13" s="779"/>
@@ -10087,7 +10111,9 @@
       <c r="K14" s="677" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="749"/>
+      <c r="L14" s="749">
+        <v>46225</v>
+      </c>
       <c r="M14" s="763"/>
       <c r="N14" s="701"/>
       <c r="P14" s="778"/>
@@ -10112,10 +10138,10 @@
         <v>59</v>
       </c>
       <c r="G15" s="632">
-        <v>42.654933999999997</v>
+        <v>42.658099999999997</v>
       </c>
       <c r="H15" s="632">
-        <v>141.905777</v>
+        <v>141.9049</v>
       </c>
       <c r="I15" s="495">
         <v>46138</v>
@@ -10126,7 +10152,9 @@
       <c r="K15" s="497" t="s">
         <v>31</v>
       </c>
-      <c r="L15" s="750"/>
+      <c r="L15" s="750">
+        <v>46228</v>
+      </c>
       <c r="M15" s="764"/>
       <c r="N15" s="702"/>
       <c r="P15" s="779"/>
@@ -10163,7 +10191,9 @@
       <c r="K16" s="497" t="s">
         <v>66</v>
       </c>
-      <c r="L16" s="747"/>
+      <c r="L16" s="747">
+        <v>46231</v>
+      </c>
       <c r="M16" s="764"/>
       <c r="N16" s="702"/>
       <c r="P16" s="779"/>
@@ -10200,7 +10230,9 @@
       <c r="K17" s="497" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="747"/>
+      <c r="L17" s="799">
+        <v>46232</v>
+      </c>
       <c r="M17" s="764"/>
       <c r="N17" s="702"/>
       <c r="P17" s="779"/>
@@ -10237,7 +10269,9 @@
       <c r="K18" s="456" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="747"/>
+      <c r="L18" s="747">
+        <v>46228</v>
+      </c>
       <c r="M18" s="764"/>
       <c r="N18" s="702"/>
       <c r="P18" s="779"/>
@@ -10274,7 +10308,9 @@
       <c r="K19" s="680" t="s">
         <v>31</v>
       </c>
-      <c r="L19" s="751"/>
+      <c r="L19" s="751">
+        <v>46223</v>
+      </c>
       <c r="M19" s="765"/>
       <c r="N19" s="705"/>
       <c r="P19" s="780"/>
@@ -10313,7 +10349,9 @@
       <c r="K20" s="492" t="s">
         <v>84</v>
       </c>
-      <c r="L20" s="744"/>
+      <c r="L20" s="744">
+        <v>46227</v>
+      </c>
       <c r="M20" s="766"/>
       <c r="N20" s="701"/>
       <c r="P20" s="778"/>
@@ -10352,7 +10390,9 @@
       <c r="K21" s="497" t="s">
         <v>31</v>
       </c>
-      <c r="L21" s="745"/>
+      <c r="L21" s="745">
+        <v>46224</v>
+      </c>
       <c r="M21" s="767"/>
       <c r="N21" s="790"/>
       <c r="P21" s="780"/>
@@ -10391,7 +10431,9 @@
       <c r="K22" s="540" t="s">
         <v>31</v>
       </c>
-      <c r="L22" s="744"/>
+      <c r="L22" s="744">
+        <v>46227</v>
+      </c>
       <c r="M22" s="763"/>
       <c r="N22" s="731"/>
       <c r="P22" s="778"/>
@@ -10428,7 +10470,9 @@
       <c r="K23" s="697" t="s">
         <v>31</v>
       </c>
-      <c r="L23" s="745"/>
+      <c r="L23" s="745">
+        <v>46226</v>
+      </c>
       <c r="M23" s="764"/>
       <c r="N23" s="702"/>
       <c r="P23" s="779"/>
@@ -10467,7 +10511,9 @@
       <c r="K24" s="445" t="s">
         <v>84</v>
       </c>
-      <c r="L24" s="745"/>
+      <c r="L24" s="745">
+        <v>46222</v>
+      </c>
       <c r="M24" s="764"/>
       <c r="N24" s="702"/>
       <c r="P24" s="779"/>
@@ -10504,7 +10550,9 @@
       <c r="K25" s="445" t="s">
         <v>84</v>
       </c>
-      <c r="L25" s="745"/>
+      <c r="L25" s="745">
+        <v>46220</v>
+      </c>
       <c r="M25" s="764"/>
       <c r="N25" s="702"/>
       <c r="P25" s="779"/>
@@ -10541,7 +10589,9 @@
       <c r="K26" s="694" t="s">
         <v>84</v>
       </c>
-      <c r="L26" s="775"/>
+      <c r="L26" s="775">
+        <v>46218</v>
+      </c>
       <c r="M26" s="768"/>
       <c r="N26" s="702"/>
       <c r="P26" s="781"/>
@@ -10578,7 +10628,9 @@
       <c r="K27" s="445" t="s">
         <v>66</v>
       </c>
-      <c r="L27" s="752"/>
+      <c r="L27" s="752">
+        <v>46223</v>
+      </c>
       <c r="M27" s="764"/>
       <c r="N27" s="796" t="s">
         <v>114</v>
@@ -10617,7 +10669,9 @@
       <c r="K28" s="792" t="s">
         <v>31</v>
       </c>
-      <c r="L28" s="745"/>
+      <c r="L28" s="745">
+        <v>46223</v>
+      </c>
       <c r="M28" s="764"/>
       <c r="N28" s="702"/>
       <c r="P28" s="781"/>
@@ -10654,7 +10708,9 @@
       <c r="K29" s="445" t="s">
         <v>84</v>
       </c>
-      <c r="L29" s="745"/>
+      <c r="L29" s="745">
+        <v>46228</v>
+      </c>
       <c r="M29" s="764"/>
       <c r="N29" s="702"/>
       <c r="P29" s="779"/>
@@ -10691,7 +10747,9 @@
       <c r="K30" s="682" t="s">
         <v>31</v>
       </c>
-      <c r="L30" s="745"/>
+      <c r="L30" s="745">
+        <v>46221</v>
+      </c>
       <c r="M30" s="764"/>
       <c r="N30" s="797" t="s">
         <v>126</v>
@@ -10730,7 +10788,9 @@
       <c r="K31" s="445" t="s">
         <v>84</v>
       </c>
-      <c r="L31" s="745"/>
+      <c r="L31" s="745">
+        <v>46224</v>
+      </c>
       <c r="M31" s="764"/>
       <c r="N31" s="702"/>
       <c r="P31" s="779"/>
@@ -10767,7 +10827,9 @@
       <c r="K32" s="445" t="s">
         <v>31</v>
       </c>
-      <c r="L32" s="745"/>
+      <c r="L32" s="745">
+        <v>46217</v>
+      </c>
       <c r="M32" s="764"/>
       <c r="N32" s="796" t="s">
         <v>135</v>
@@ -10803,10 +10865,12 @@
       <c r="J33" s="444">
         <v>46154</v>
       </c>
-      <c r="K33" s="445" t="s">
-        <v>84</v>
-      </c>
-      <c r="L33" s="745"/>
+      <c r="K33" s="800" t="s">
+        <v>140</v>
+      </c>
+      <c r="L33" s="745">
+        <v>46227</v>
+      </c>
       <c r="M33" s="764"/>
       <c r="N33" s="702"/>
       <c r="P33" s="779"/>
@@ -10817,16 +10881,16 @@
       </c>
       <c r="B34" s="562"/>
       <c r="C34" s="503" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="563" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E34" s="575" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F34" s="563" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G34" s="632">
         <v>43.756300000000003</v>
@@ -10843,10 +10907,12 @@
       <c r="K34" s="445" t="s">
         <v>84</v>
       </c>
-      <c r="L34" s="745"/>
+      <c r="L34" s="745">
+        <v>46224</v>
+      </c>
       <c r="M34" s="764"/>
       <c r="N34" s="793" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P34" s="779"/>
     </row>
@@ -10856,16 +10922,16 @@
       </c>
       <c r="B35" s="786"/>
       <c r="C35" s="504" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D35" s="569" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" s="569" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F35" s="569" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G35" s="634">
         <v>43.696800000000003</v>
@@ -10882,7 +10948,9 @@
       <c r="K35" s="683" t="s">
         <v>84</v>
       </c>
-      <c r="L35" s="753"/>
+      <c r="L35" s="753">
+        <v>46226</v>
+      </c>
       <c r="M35" s="765"/>
       <c r="N35" s="798"/>
       <c r="P35" s="780"/>
@@ -10892,19 +10960,19 @@
         <v>29</v>
       </c>
       <c r="B36" s="557" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C36" s="558" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D36" s="558" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E36" s="558" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F36" s="558" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G36" s="641">
         <v>44.368572</v>
@@ -10919,9 +10987,11 @@
         <v>45432</v>
       </c>
       <c r="K36" s="688" t="s">
-        <v>153</v>
-      </c>
-      <c r="L36" s="744"/>
+        <v>154</v>
+      </c>
+      <c r="L36" s="744">
+        <v>46225</v>
+      </c>
       <c r="M36" s="763"/>
       <c r="N36" s="784"/>
       <c r="P36" s="778"/>
@@ -10934,16 +11004,16 @@
         <v>85</v>
       </c>
       <c r="C37" s="563" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D37" s="563" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E37" s="479" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F37" s="563" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G37" s="771">
         <v>44.000500000000002</v>
@@ -10958,9 +11028,11 @@
         <v>45431</v>
       </c>
       <c r="K37" s="686" t="s">
-        <v>153</v>
-      </c>
-      <c r="L37" s="746"/>
+        <v>154</v>
+      </c>
+      <c r="L37" s="746">
+        <v>46223</v>
+      </c>
       <c r="M37" s="765"/>
       <c r="N37" s="703"/>
       <c r="P37" s="780"/>
@@ -10970,19 +11042,19 @@
         <v>31</v>
       </c>
       <c r="B38" s="557" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C38" s="788" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D38" s="579" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E38" s="579" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F38" s="789" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G38" s="630">
         <v>43.803699999999999</v>
@@ -10997,9 +11069,11 @@
         <v>46155</v>
       </c>
       <c r="K38" s="452" t="s">
-        <v>162</v>
-      </c>
-      <c r="L38" s="754"/>
+        <v>163</v>
+      </c>
+      <c r="L38" s="754">
+        <v>46221</v>
+      </c>
       <c r="M38" s="763"/>
       <c r="N38" s="706"/>
       <c r="P38" s="779"/>
@@ -11010,16 +11084,16 @@
       </c>
       <c r="B39" s="659"/>
       <c r="C39" s="412" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D39" s="474" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E39" s="474" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F39" s="474" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G39" s="644">
         <v>43.831299999999999</v>
@@ -11036,7 +11110,9 @@
       <c r="K39" s="688" t="s">
         <v>46</v>
       </c>
-      <c r="L39" s="747"/>
+      <c r="L39" s="747">
+        <v>46218</v>
+      </c>
       <c r="M39" s="764"/>
       <c r="N39" s="702"/>
       <c r="P39" s="779"/>
@@ -11046,19 +11122,19 @@
         <v>33</v>
       </c>
       <c r="B40" s="659" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" s="412" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" s="474" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" s="474" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F40" s="474" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G40" s="632">
         <v>43.392699999999998</v>
@@ -11073,9 +11149,11 @@
         <v>46158</v>
       </c>
       <c r="K40" s="456" t="s">
-        <v>162</v>
-      </c>
-      <c r="L40" s="747"/>
+        <v>163</v>
+      </c>
+      <c r="L40" s="747">
+        <v>46216</v>
+      </c>
       <c r="M40" s="764"/>
       <c r="N40" s="702"/>
       <c r="P40" s="779"/>
@@ -11086,16 +11164,16 @@
       </c>
       <c r="B41" s="659"/>
       <c r="C41" s="412" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D41" s="474" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E41" s="474" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F41" s="474" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G41" s="632">
         <v>43.430799999999998</v>
@@ -11110,9 +11188,11 @@
         <v>46170</v>
       </c>
       <c r="K41" s="456" t="s">
-        <v>162</v>
-      </c>
-      <c r="L41" s="747"/>
+        <v>163</v>
+      </c>
+      <c r="L41" s="747">
+        <v>46216</v>
+      </c>
       <c r="M41" s="764"/>
       <c r="N41" s="702"/>
       <c r="P41" s="779"/>
@@ -11123,16 +11203,16 @@
       </c>
       <c r="B42" s="664"/>
       <c r="C42" s="412" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D42" s="474" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E42" s="474" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F42" s="474" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G42" s="632">
         <v>43.703099999999999</v>
@@ -11147,9 +11227,11 @@
         <v>46155</v>
       </c>
       <c r="K42" s="456" t="s">
-        <v>162</v>
-      </c>
-      <c r="L42" s="747"/>
+        <v>163</v>
+      </c>
+      <c r="L42" s="747">
+        <v>46220</v>
+      </c>
       <c r="M42" s="764"/>
       <c r="N42" s="702"/>
       <c r="P42" s="779"/>
@@ -11160,16 +11242,16 @@
       </c>
       <c r="B43" s="659"/>
       <c r="C43" s="412" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D43" s="474" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E43" s="474" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F43" s="474" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G43" s="632">
         <v>43.6995</v>
@@ -11184,9 +11266,11 @@
         <v>46162</v>
       </c>
       <c r="K43" s="456" t="s">
-        <v>183</v>
-      </c>
-      <c r="L43" s="747"/>
+        <v>184</v>
+      </c>
+      <c r="L43" s="747">
+        <v>46221</v>
+      </c>
       <c r="M43" s="764"/>
       <c r="N43" s="702"/>
       <c r="P43" s="779"/>
@@ -11197,16 +11281,16 @@
       </c>
       <c r="B44" s="659"/>
       <c r="C44" s="412" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D44" s="474" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" s="474" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F44" s="474" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G44" s="632">
         <v>43.841327999999997</v>
@@ -11221,9 +11305,11 @@
         <v>46155</v>
       </c>
       <c r="K44" s="456" t="s">
-        <v>188</v>
-      </c>
-      <c r="L44" s="747"/>
+        <v>154</v>
+      </c>
+      <c r="L44" s="747">
+        <v>46221</v>
+      </c>
       <c r="M44" s="764"/>
       <c r="N44" s="736"/>
       <c r="P44" s="779"/>
@@ -11258,9 +11344,11 @@
         <v>46159</v>
       </c>
       <c r="K45" s="456" t="s">
-        <v>188</v>
-      </c>
-      <c r="L45" s="755"/>
+        <v>154</v>
+      </c>
+      <c r="L45" s="755">
+        <v>46223</v>
+      </c>
       <c r="M45" s="764"/>
       <c r="N45" s="707"/>
       <c r="P45" s="779"/>
@@ -11295,9 +11383,11 @@
         <v>46167</v>
       </c>
       <c r="K46" s="456" t="s">
-        <v>183</v>
-      </c>
-      <c r="L46" s="755"/>
+        <v>184</v>
+      </c>
+      <c r="L46" s="755">
+        <v>46226</v>
+      </c>
       <c r="M46" s="764"/>
       <c r="N46" s="707"/>
       <c r="P46" s="779"/>
@@ -11332,9 +11422,11 @@
         <v>46161</v>
       </c>
       <c r="K47" s="686" t="s">
-        <v>188</v>
-      </c>
-      <c r="L47" s="756"/>
+        <v>154</v>
+      </c>
+      <c r="L47" s="756">
+        <v>46221</v>
+      </c>
       <c r="M47" s="765"/>
       <c r="N47" s="794" t="s">
         <v>201</v>
@@ -11441,12 +11533,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="P4:P7"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="N6:N7"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:G7"/>
@@ -11459,6 +11545,12 @@
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
+    <mergeCell ref="P4:P7"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="N6:N7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11474,14 +11566,14 @@
   <dimension ref="A1:N54"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="4" width="13.375" customWidth="1"/>
-    <col min="5" max="5" width="0.375" customWidth="1"/>
-    <col min="6" max="6" width="42.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="0.5" customWidth="1"/>
+    <col min="6" max="6" width="42.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="9" max="9" width="11.625" customWidth="1"/>
-    <col min="10" max="10" width="14.625" customWidth="1"/>
-    <col min="11" max="11" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
@@ -11489,112 +11581,112 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N1" s="380">
         <f ca="1">NOW()</f>
-        <v>46206.598910995373</v>
+        <v>46246.77676990741</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A2" s="882" t="s">
-        <v>470</v>
-      </c>
-      <c r="B2" s="882"/>
-      <c r="C2" s="882"/>
-      <c r="D2" s="882"/>
-      <c r="E2" s="882"/>
-      <c r="F2" s="882"/>
-      <c r="G2" s="882"/>
-      <c r="H2" s="882"/>
+      <c r="A2" s="885" t="s">
+        <v>471</v>
+      </c>
+      <c r="B2" s="885"/>
+      <c r="C2" s="885"/>
+      <c r="D2" s="885"/>
+      <c r="E2" s="885"/>
+      <c r="F2" s="885"/>
+      <c r="G2" s="885"/>
+      <c r="H2" s="885"/>
       <c r="I2" s="326" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J2" s="326" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K2" s="326" t="s">
-        <v>473</v>
-      </c>
-      <c r="L2" s="881" t="s">
         <v>474</v>
+      </c>
+      <c r="L2" s="884" t="s">
+        <v>475</v>
       </c>
       <c r="M2" s="307"/>
       <c r="N2" s="307"/>
     </row>
     <row r="3" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="813" t="s">
+      <c r="A3" s="805" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="825" t="s">
+      <c r="B3" s="806" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="813" t="s">
+      <c r="C3" s="805" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="813" t="s">
+      <c r="D3" s="805" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="883" t="s">
-        <v>344</v>
-      </c>
-      <c r="F3" s="813" t="s">
+      <c r="E3" s="886" t="s">
+        <v>345</v>
+      </c>
+      <c r="F3" s="805" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="825" t="s">
-        <v>345</v>
-      </c>
-      <c r="H3" s="884" t="s">
+      <c r="G3" s="806" t="s">
+        <v>346</v>
+      </c>
+      <c r="H3" s="887" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="884" t="s">
+      <c r="I3" s="887" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="884" t="s">
+      <c r="J3" s="887" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="885" t="s">
-        <v>475</v>
-      </c>
-      <c r="L3" s="881"/>
-      <c r="M3" s="882" t="s">
+      <c r="K3" s="888" t="s">
         <v>476</v>
       </c>
-      <c r="N3" s="882" t="s">
+      <c r="L3" s="884"/>
+      <c r="M3" s="885" t="s">
         <v>477</v>
       </c>
+      <c r="N3" s="885" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A4" s="813"/>
-      <c r="B4" s="825"/>
-      <c r="C4" s="813"/>
-      <c r="D4" s="813"/>
-      <c r="E4" s="883"/>
-      <c r="F4" s="813"/>
-      <c r="G4" s="825"/>
-      <c r="H4" s="813"/>
-      <c r="I4" s="813"/>
-      <c r="J4" s="813"/>
-      <c r="K4" s="886"/>
-      <c r="L4" s="881"/>
-      <c r="M4" s="882"/>
-      <c r="N4" s="882"/>
+      <c r="A4" s="805"/>
+      <c r="B4" s="806"/>
+      <c r="C4" s="805"/>
+      <c r="D4" s="805"/>
+      <c r="E4" s="886"/>
+      <c r="F4" s="805"/>
+      <c r="G4" s="806"/>
+      <c r="H4" s="805"/>
+      <c r="I4" s="805"/>
+      <c r="J4" s="805"/>
+      <c r="K4" s="889"/>
+      <c r="L4" s="884"/>
+      <c r="M4" s="885"/>
+      <c r="N4" s="885"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A5" s="813"/>
-      <c r="B5" s="825"/>
-      <c r="C5" s="813"/>
-      <c r="D5" s="813"/>
-      <c r="E5" s="883"/>
-      <c r="F5" s="813"/>
-      <c r="G5" s="825"/>
-      <c r="H5" s="813"/>
-      <c r="I5" s="813"/>
-      <c r="J5" s="813"/>
-      <c r="K5" s="887"/>
-      <c r="L5" s="881"/>
-      <c r="M5" s="882"/>
-      <c r="N5" s="882"/>
+      <c r="A5" s="805"/>
+      <c r="B5" s="806"/>
+      <c r="C5" s="805"/>
+      <c r="D5" s="805"/>
+      <c r="E5" s="886"/>
+      <c r="F5" s="805"/>
+      <c r="G5" s="806"/>
+      <c r="H5" s="805"/>
+      <c r="I5" s="805"/>
+      <c r="J5" s="805"/>
+      <c r="K5" s="890"/>
+      <c r="L5" s="884"/>
+      <c r="M5" s="885"/>
+      <c r="N5" s="885"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A6" s="150">
@@ -11610,13 +11702,13 @@
         <v>28</v>
       </c>
       <c r="E6" s="341" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F6" s="341" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="292" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H6" s="309" t="s">
         <v>29</v>
@@ -11631,7 +11723,7 @@
         <v>29</v>
       </c>
       <c r="L6" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M6" s="307"/>
       <c r="N6" s="307"/>
@@ -11644,34 +11736,34 @@
         <v>32</v>
       </c>
       <c r="C7" s="342" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D7" s="342" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="342" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F7" s="342" t="s">
+        <v>352</v>
+      </c>
+      <c r="G7" s="293" t="s">
         <v>351</v>
       </c>
-      <c r="G7" s="293" t="s">
-        <v>350</v>
-      </c>
       <c r="H7" s="309" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I7" s="309" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J7" s="310" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K7" s="310" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L7" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M7" s="307"/>
       <c r="N7" s="307"/>
@@ -11681,7 +11773,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="390" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C8" s="343" t="s">
         <v>37</v>
@@ -11690,13 +11782,13 @@
         <v>38</v>
       </c>
       <c r="E8" s="343" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F8" s="343" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="294" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H8" s="309" t="s">
         <v>39</v>
@@ -11711,7 +11803,7 @@
         <v>39</v>
       </c>
       <c r="L8" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M8" s="307"/>
       <c r="N8" s="307"/>
@@ -11730,13 +11822,13 @@
         <v>43</v>
       </c>
       <c r="E9" s="344" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F9" s="344" t="s">
+        <v>357</v>
+      </c>
+      <c r="G9" s="295" t="s">
         <v>356</v>
-      </c>
-      <c r="G9" s="295" t="s">
-        <v>355</v>
       </c>
       <c r="H9" s="311" t="s">
         <v>44</v>
@@ -11751,7 +11843,7 @@
         <v>44</v>
       </c>
       <c r="L9" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M9" s="307"/>
       <c r="N9" s="307"/>
@@ -11770,13 +11862,13 @@
         <v>48</v>
       </c>
       <c r="E10" s="345" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F10" s="345" t="s">
+        <v>360</v>
+      </c>
+      <c r="G10" s="296" t="s">
         <v>359</v>
-      </c>
-      <c r="G10" s="296" t="s">
-        <v>358</v>
       </c>
       <c r="H10" s="311" t="s">
         <v>49</v>
@@ -11791,7 +11883,7 @@
         <v>49</v>
       </c>
       <c r="L10" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M10" s="307"/>
       <c r="N10" s="307"/>
@@ -11801,7 +11893,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="391" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C11" s="346" t="s">
         <v>47</v>
@@ -11810,13 +11902,13 @@
         <v>52</v>
       </c>
       <c r="E11" s="346" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F11" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="G11" s="297" t="s">
         <v>362</v>
-      </c>
-      <c r="G11" s="297" t="s">
-        <v>361</v>
       </c>
       <c r="H11" s="311" t="s">
         <v>53</v>
@@ -11831,7 +11923,7 @@
         <v>53</v>
       </c>
       <c r="L11" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M11" s="307"/>
       <c r="N11" s="307"/>
@@ -11850,13 +11942,13 @@
         <v>57</v>
       </c>
       <c r="E12" s="347" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F12" s="347" t="s">
+        <v>366</v>
+      </c>
+      <c r="G12" s="298" t="s">
         <v>365</v>
-      </c>
-      <c r="G12" s="298" t="s">
-        <v>364</v>
       </c>
       <c r="H12" s="313" t="s">
         <v>58</v>
@@ -11871,7 +11963,7 @@
         <v>58</v>
       </c>
       <c r="L12" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M12" s="307"/>
       <c r="N12" s="307"/>
@@ -11884,34 +11976,34 @@
         <v>60</v>
       </c>
       <c r="C13" s="348" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D13" s="348" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E13" s="348" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F13" s="348" t="s">
+        <v>371</v>
+      </c>
+      <c r="G13" s="299" t="s">
         <v>370</v>
       </c>
-      <c r="G13" s="299" t="s">
-        <v>369</v>
-      </c>
       <c r="H13" s="313" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I13" s="313" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J13" s="314" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K13" s="358" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L13" s="307" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M13" s="307"/>
       <c r="N13" s="307"/>
@@ -11928,28 +12020,28 @@
         <v>63</v>
       </c>
       <c r="E14" s="348" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F14" s="348" t="s">
+        <v>376</v>
+      </c>
+      <c r="G14" s="299" t="s">
         <v>375</v>
       </c>
-      <c r="G14" s="299" t="s">
+      <c r="H14" s="323" t="s">
         <v>374</v>
       </c>
-      <c r="H14" s="323" t="s">
-        <v>373</v>
-      </c>
       <c r="I14" s="313" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J14" s="314" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K14" s="314" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L14" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M14" s="307"/>
       <c r="N14" s="307"/>
@@ -11963,31 +12055,31 @@
         <v>67</v>
       </c>
       <c r="D15" s="348" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E15" s="348" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F15" s="348" t="s">
+        <v>380</v>
+      </c>
+      <c r="G15" s="299" t="s">
         <v>379</v>
       </c>
-      <c r="G15" s="299" t="s">
-        <v>378</v>
-      </c>
       <c r="H15" s="313" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I15" s="313" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J15" s="314" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K15" s="314" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L15" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M15" s="307"/>
       <c r="N15" s="307"/>
@@ -12004,28 +12096,28 @@
         <v>72</v>
       </c>
       <c r="E16" s="348" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F16" s="348" t="s">
+        <v>384</v>
+      </c>
+      <c r="G16" s="299" t="s">
         <v>383</v>
       </c>
-      <c r="G16" s="299" t="s">
-        <v>382</v>
-      </c>
       <c r="H16" s="313" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I16" s="313" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J16" s="314" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K16" s="314" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L16" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M16" s="307"/>
       <c r="N16" s="307"/>
@@ -12035,7 +12127,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="390" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C17" s="349" t="s">
         <v>75</v>
@@ -12044,13 +12136,13 @@
         <v>76</v>
       </c>
       <c r="E17" s="349" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F17" s="349" t="s">
         <v>78</v>
       </c>
       <c r="G17" s="300" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H17" s="313" t="s">
         <v>77</v>
@@ -12065,7 +12157,7 @@
         <v>77</v>
       </c>
       <c r="L17" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M17" s="307"/>
       <c r="N17" s="307"/>
@@ -12084,31 +12176,31 @@
         <v>81</v>
       </c>
       <c r="E18" s="372" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F18" s="372" t="s">
         <v>83</v>
       </c>
       <c r="G18" s="373" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H18" s="374" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I18" s="374" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J18" s="375" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K18" s="376" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L18" s="365" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M18" s="307" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N18" s="307"/>
     </row>
@@ -12117,37 +12209,37 @@
         <v>14</v>
       </c>
       <c r="B19" s="357" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C19" s="363" t="s">
         <v>86</v>
       </c>
       <c r="D19" s="363" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E19" s="363" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F19" s="363" t="s">
+        <v>391</v>
+      </c>
+      <c r="G19" s="364" t="s">
         <v>390</v>
       </c>
-      <c r="G19" s="364" t="s">
-        <v>389</v>
-      </c>
       <c r="H19" s="363" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I19" s="363" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J19" s="363" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K19" s="363" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L19" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M19" s="307"/>
       <c r="N19" s="307"/>
@@ -12158,33 +12250,33 @@
       </c>
       <c r="B20" s="330"/>
       <c r="C20" s="329" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D20" s="329" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E20" s="329"/>
       <c r="F20" s="329" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G20" s="328"/>
       <c r="H20" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I20" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J20" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K20" s="359" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L20" s="307" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M20" s="307" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N20" s="307"/>
     </row>
@@ -12194,33 +12286,33 @@
       </c>
       <c r="B21" s="330"/>
       <c r="C21" s="329" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D21" s="329" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E21" s="329"/>
       <c r="F21" s="329" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G21" s="328"/>
       <c r="H21" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I21" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J21" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K21" s="360" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L21" s="307" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M21" s="307" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N21" s="307"/>
     </row>
@@ -12229,31 +12321,31 @@
         <v>17</v>
       </c>
       <c r="B22" s="392" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C22" s="329" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D22" s="350"/>
       <c r="E22" s="350"/>
       <c r="F22" s="350" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G22" s="325"/>
       <c r="H22" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I22" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J22" s="328" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K22" s="361" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L22" s="307" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M22" s="307"/>
       <c r="N22" s="307"/>
@@ -12269,16 +12361,16 @@
         <v>91</v>
       </c>
       <c r="D23" s="366" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E23" s="366" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F23" s="366" t="s">
+        <v>395</v>
+      </c>
+      <c r="G23" s="368" t="s">
         <v>394</v>
-      </c>
-      <c r="G23" s="368" t="s">
-        <v>393</v>
       </c>
       <c r="H23" s="369" t="s">
         <v>93</v>
@@ -12293,7 +12385,7 @@
         <v>93</v>
       </c>
       <c r="L23" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M23" s="307"/>
       <c r="N23" s="307"/>
@@ -12307,13 +12399,13 @@
         <v>95</v>
       </c>
       <c r="E24" s="382" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F24" s="382" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G24" s="383" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H24" s="384" t="s">
         <v>96</v>
@@ -12325,13 +12417,13 @@
         <v>96</v>
       </c>
       <c r="K24" s="362" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L24" s="307" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M24" s="307" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N24" s="307"/>
     </row>
@@ -12340,22 +12432,22 @@
         <v>19</v>
       </c>
       <c r="B25" s="339" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C25" s="371" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D25" s="371" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="371" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F25" s="371" t="s">
+        <v>399</v>
+      </c>
+      <c r="G25" s="367" t="s">
         <v>398</v>
-      </c>
-      <c r="G25" s="367" t="s">
-        <v>397</v>
       </c>
       <c r="H25" s="377" t="s">
         <v>101</v>
@@ -12370,7 +12462,7 @@
         <v>101</v>
       </c>
       <c r="L25" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M25" s="307"/>
       <c r="N25" s="307"/>
@@ -12381,19 +12473,19 @@
       </c>
       <c r="B26" s="339"/>
       <c r="C26" s="371" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D26" s="371" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E26" s="371" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F26" s="371" t="s">
+        <v>403</v>
+      </c>
+      <c r="G26" s="367" t="s">
         <v>402</v>
-      </c>
-      <c r="G26" s="367" t="s">
-        <v>401</v>
       </c>
       <c r="H26" s="378" t="s">
         <v>104</v>
@@ -12408,7 +12500,7 @@
         <v>104</v>
       </c>
       <c r="L26" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M26" s="307"/>
       <c r="N26" s="307"/>
@@ -12419,34 +12511,34 @@
       </c>
       <c r="B27" s="339"/>
       <c r="C27" s="371" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D27" s="371" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E27" s="371" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F27" s="371" t="s">
+        <v>405</v>
+      </c>
+      <c r="G27" s="367" t="s">
         <v>404</v>
       </c>
-      <c r="G27" s="367" t="s">
-        <v>403</v>
-      </c>
       <c r="H27" s="369" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I27" s="369" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J27" s="370" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K27" s="370" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L27" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M27" s="307"/>
       <c r="N27" s="307"/>
@@ -12457,19 +12549,19 @@
       </c>
       <c r="B28" s="339"/>
       <c r="C28" s="352" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D28" s="352" t="s">
         <v>111</v>
       </c>
       <c r="E28" s="352" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F28" s="352" t="s">
+        <v>410</v>
+      </c>
+      <c r="G28" s="301" t="s">
         <v>409</v>
-      </c>
-      <c r="G28" s="301" t="s">
-        <v>408</v>
       </c>
       <c r="H28" s="317" t="s">
         <v>216</v>
@@ -12484,7 +12576,7 @@
         <v>216</v>
       </c>
       <c r="L28" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M28" s="307"/>
       <c r="N28" s="307"/>
@@ -12495,22 +12587,22 @@
       </c>
       <c r="B29" s="339"/>
       <c r="C29" s="352" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D29" s="352" t="s">
         <v>115</v>
       </c>
       <c r="E29" s="352" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F29" s="352" t="s">
+        <v>415</v>
+      </c>
+      <c r="G29" s="301" t="s">
         <v>414</v>
       </c>
-      <c r="G29" s="301" t="s">
+      <c r="H29" s="319" t="s">
         <v>413</v>
-      </c>
-      <c r="H29" s="319" t="s">
-        <v>412</v>
       </c>
       <c r="I29" s="315" t="s">
         <v>116</v>
@@ -12522,7 +12614,7 @@
         <v>116</v>
       </c>
       <c r="L29" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M29" s="307"/>
       <c r="N29" s="307"/>
@@ -12533,19 +12625,19 @@
       </c>
       <c r="B30" s="339"/>
       <c r="C30" s="371" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D30" s="371" t="s">
         <v>119</v>
       </c>
       <c r="E30" s="371" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F30" s="371" t="s">
+        <v>418</v>
+      </c>
+      <c r="G30" s="367" t="s">
         <v>417</v>
-      </c>
-      <c r="G30" s="367" t="s">
-        <v>416</v>
       </c>
       <c r="H30" s="369" t="s">
         <v>120</v>
@@ -12560,7 +12652,7 @@
         <v>120</v>
       </c>
       <c r="L30" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M30" s="307"/>
       <c r="N30" s="307"/>
@@ -12571,25 +12663,25 @@
       </c>
       <c r="B31" s="339"/>
       <c r="C31" s="352" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D31" s="352" t="s">
         <v>123</v>
       </c>
       <c r="E31" s="352" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F31" s="352" t="s">
+        <v>421</v>
+      </c>
+      <c r="G31" s="301" t="s">
         <v>420</v>
       </c>
-      <c r="G31" s="301" t="s">
-        <v>419</v>
-      </c>
       <c r="H31" s="317" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I31" s="317" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J31" s="322" t="s">
         <v>124</v>
@@ -12598,7 +12690,7 @@
         <v>124</v>
       </c>
       <c r="L31" s="307" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M31" s="307"/>
       <c r="N31" s="307"/>
@@ -12609,19 +12701,19 @@
       </c>
       <c r="B32" s="339"/>
       <c r="C32" s="352" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D32" s="352" t="s">
         <v>128</v>
       </c>
       <c r="E32" s="352" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F32" s="352" t="s">
+        <v>425</v>
+      </c>
+      <c r="G32" s="301" t="s">
         <v>424</v>
-      </c>
-      <c r="G32" s="301" t="s">
-        <v>423</v>
       </c>
       <c r="H32" s="317" t="s">
         <v>129</v>
@@ -12636,7 +12728,7 @@
         <v>129</v>
       </c>
       <c r="L32" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M32" s="307"/>
       <c r="N32" s="307"/>
@@ -12647,19 +12739,19 @@
       </c>
       <c r="B33" s="339"/>
       <c r="C33" s="371" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D33" s="371" t="s">
         <v>132</v>
       </c>
       <c r="E33" s="371" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F33" s="371" t="s">
+        <v>427</v>
+      </c>
+      <c r="G33" s="367" t="s">
         <v>426</v>
-      </c>
-      <c r="G33" s="367" t="s">
-        <v>425</v>
       </c>
       <c r="H33" s="369" t="s">
         <v>218</v>
@@ -12674,7 +12766,7 @@
         <v>218</v>
       </c>
       <c r="L33" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M33" s="307"/>
       <c r="N33" s="307"/>
@@ -12685,25 +12777,25 @@
       </c>
       <c r="B34" s="339"/>
       <c r="C34" s="352" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D34" s="352" t="s">
         <v>137</v>
       </c>
       <c r="E34" s="352" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F34" s="352" t="s">
+        <v>431</v>
+      </c>
+      <c r="G34" s="301" t="s">
         <v>430</v>
       </c>
-      <c r="G34" s="301" t="s">
-        <v>429</v>
-      </c>
       <c r="H34" s="317" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I34" s="317" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J34" s="322" t="s">
         <v>138</v>
@@ -12712,7 +12804,7 @@
         <v>138</v>
       </c>
       <c r="L34" s="307" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M34" s="307"/>
       <c r="N34" s="307"/>
@@ -12723,34 +12815,34 @@
       </c>
       <c r="B35" s="339"/>
       <c r="C35" s="371" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D35" s="371" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E35" s="371" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F35" s="371" t="s">
+        <v>434</v>
+      </c>
+      <c r="G35" s="367" t="s">
         <v>433</v>
       </c>
-      <c r="G35" s="367" t="s">
-        <v>432</v>
-      </c>
       <c r="H35" s="369" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I35" s="369" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J35" s="370" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K35" s="375" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L35" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M35" s="307"/>
       <c r="N35" s="307"/>
@@ -12760,37 +12852,37 @@
         <v>30</v>
       </c>
       <c r="B36" s="394" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C36" s="353" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D36" s="353" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" s="353" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F36" s="353" t="s">
+        <v>437</v>
+      </c>
+      <c r="G36" s="302" t="s">
         <v>436</v>
       </c>
-      <c r="G36" s="302" t="s">
-        <v>435</v>
-      </c>
       <c r="H36" s="319" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I36" s="315" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J36" s="322" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K36" s="327" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L36" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M36" s="307"/>
       <c r="N36" s="307"/>
@@ -12800,35 +12892,35 @@
         <v>31</v>
       </c>
       <c r="B37" s="338" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C37" s="351" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D37" s="351" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E37" s="351"/>
       <c r="F37" s="351" t="s">
+        <v>440</v>
+      </c>
+      <c r="G37" s="308" t="s">
         <v>439</v>
       </c>
-      <c r="G37" s="308" t="s">
-        <v>438</v>
-      </c>
       <c r="H37" s="317" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I37" s="317" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J37" s="318" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K37" s="327" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L37" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M37" s="307"/>
       <c r="N37" s="307"/>
@@ -12841,32 +12933,32 @@
         <v>85</v>
       </c>
       <c r="C38" s="352" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D38" s="352" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E38" s="352"/>
       <c r="F38" s="352" t="s">
+        <v>157</v>
+      </c>
+      <c r="G38" s="400" t="s">
+        <v>441</v>
+      </c>
+      <c r="H38" s="351" t="s">
         <v>156</v>
       </c>
-      <c r="G38" s="400" t="s">
-        <v>440</v>
-      </c>
-      <c r="H38" s="351" t="s">
-        <v>155</v>
-      </c>
       <c r="I38" s="351" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J38" s="401" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K38" s="402" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L38" s="403" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M38" s="307"/>
       <c r="N38" s="307"/>
@@ -12874,7 +12966,7 @@
     <row r="39" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A39" s="387"/>
       <c r="B39" s="392" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C39" s="388"/>
       <c r="D39" s="388"/>
@@ -12894,37 +12986,37 @@
         <v>33</v>
       </c>
       <c r="B40" s="338" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C40" s="366" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D40" s="366" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E40" s="366" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F40" s="366" t="s">
+        <v>445</v>
+      </c>
+      <c r="G40" s="368" t="s">
         <v>444</v>
       </c>
-      <c r="G40" s="368" t="s">
-        <v>443</v>
-      </c>
       <c r="H40" s="369" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I40" s="369" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J40" s="370" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K40" s="370" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L40" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M40" s="307"/>
       <c r="N40" s="307"/>
@@ -12935,34 +13027,34 @@
       </c>
       <c r="B41" s="339"/>
       <c r="C41" s="354" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D41" s="354" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E41" s="354" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F41" s="354" t="s">
+        <v>447</v>
+      </c>
+      <c r="G41" s="303" t="s">
         <v>446</v>
       </c>
-      <c r="G41" s="303" t="s">
-        <v>445</v>
-      </c>
       <c r="H41" s="319" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I41" s="315" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J41" s="316" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K41" s="322" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L41" s="307" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M41" s="307"/>
       <c r="N41" s="307"/>
@@ -12972,37 +13064,37 @@
         <v>35</v>
       </c>
       <c r="B42" s="339" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C42" s="352" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D42" s="352" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E42" s="352" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F42" s="352" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G42" s="301" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H42" s="317" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I42" s="317" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J42" s="318" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K42" s="318" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L42" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M42" s="307"/>
       <c r="N42" s="307"/>
@@ -13013,34 +13105,34 @@
       </c>
       <c r="B43" s="339"/>
       <c r="C43" s="352" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D43" s="352" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E43" s="352" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F43" s="352" t="s">
+        <v>452</v>
+      </c>
+      <c r="G43" s="301" t="s">
         <v>451</v>
       </c>
-      <c r="G43" s="301" t="s">
-        <v>450</v>
-      </c>
       <c r="H43" s="317" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I43" s="317" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J43" s="322" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K43" s="362" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L43" s="307" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M43" s="307"/>
       <c r="N43" s="307"/>
@@ -13051,34 +13143,34 @@
       </c>
       <c r="B44" s="340"/>
       <c r="C44" s="355" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D44" s="355" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E44" s="355" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F44" s="355" t="s">
+        <v>456</v>
+      </c>
+      <c r="G44" s="304" t="s">
         <v>455</v>
       </c>
-      <c r="G44" s="304" t="s">
+      <c r="H44" s="319" t="s">
         <v>454</v>
       </c>
-      <c r="H44" s="319" t="s">
-        <v>453</v>
-      </c>
       <c r="I44" s="315" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J44" s="316" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K44" s="316" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L44" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M44" s="307"/>
       <c r="N44" s="307"/>
@@ -13089,34 +13181,34 @@
       </c>
       <c r="B45" s="339"/>
       <c r="C45" s="352" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D45" s="352" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E45" s="352" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F45" s="352" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G45" s="305" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H45" s="320" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I45" s="320" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J45" s="321" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K45" s="321" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L45" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M45" s="307"/>
       <c r="N45" s="307"/>
@@ -13127,34 +13219,34 @@
       </c>
       <c r="B46" s="339"/>
       <c r="C46" s="371" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D46" s="371" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E46" s="371" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F46" s="371" t="s">
+        <v>460</v>
+      </c>
+      <c r="G46" s="367" t="s">
         <v>459</v>
       </c>
-      <c r="G46" s="367" t="s">
-        <v>458</v>
-      </c>
       <c r="H46" s="369" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I46" s="369" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J46" s="370" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K46" s="370" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L46" s="365" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M46" s="307"/>
       <c r="N46" s="307"/>
@@ -13165,34 +13257,34 @@
       </c>
       <c r="B47" s="339"/>
       <c r="C47" s="352" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D47" s="352" t="s">
         <v>190</v>
       </c>
       <c r="E47" s="352" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F47" s="352" t="s">
+        <v>463</v>
+      </c>
+      <c r="G47" s="301" t="s">
         <v>462</v>
       </c>
-      <c r="G47" s="301" t="s">
-        <v>461</v>
-      </c>
       <c r="H47" s="317" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I47" s="317" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J47" s="318" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K47" s="322" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L47" s="307" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M47" s="307"/>
       <c r="N47" s="307"/>
@@ -13203,19 +13295,19 @@
       </c>
       <c r="B48" s="339"/>
       <c r="C48" s="352" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D48" s="352" t="s">
         <v>194</v>
       </c>
       <c r="E48" s="352" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F48" s="352" t="s">
+        <v>466</v>
+      </c>
+      <c r="G48" s="301" t="s">
         <v>465</v>
-      </c>
-      <c r="G48" s="301" t="s">
-        <v>464</v>
       </c>
       <c r="H48" s="317" t="s">
         <v>195</v>
@@ -13230,7 +13322,7 @@
         <v>195</v>
       </c>
       <c r="L48" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M48" s="307"/>
       <c r="N48" s="307"/>
@@ -13240,7 +13332,7 @@
         <v>42</v>
       </c>
       <c r="B49" s="404" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C49" s="356" t="s">
         <v>197</v>
@@ -13249,13 +13341,13 @@
         <v>198</v>
       </c>
       <c r="E49" s="356" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F49" s="356" t="s">
+        <v>469</v>
+      </c>
+      <c r="G49" s="306" t="s">
         <v>468</v>
-      </c>
-      <c r="G49" s="306" t="s">
-        <v>467</v>
       </c>
       <c r="H49" s="319" t="s">
         <v>199</v>
@@ -13270,34 +13362,34 @@
         <v>199</v>
       </c>
       <c r="L49" s="307" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M49" s="307"/>
       <c r="N49" s="307"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A50" s="386" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B50" s="408" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.15">
       <c r="C51" s="365"/>
       <c r="D51" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.15">
       <c r="C52" s="307"/>
       <c r="D52" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.15">
       <c r="C54" s="405" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D54" s="406"/>
       <c r="E54" s="406"/>
@@ -13345,21 +13437,21 @@
   <dimension ref="A1:P57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.375" style="523" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="523" customWidth="1"/>
     <col min="2" max="2" width="9" style="523"/>
-    <col min="3" max="4" width="13.375" style="523" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="523" customWidth="1"/>
-    <col min="6" max="6" width="36.625" style="523" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="523" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="523" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="523" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="523" customWidth="1"/>
+    <col min="6" max="6" width="36.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.375" style="28" customWidth="1"/>
+    <col min="13" max="13" width="16.5" style="28" customWidth="1"/>
     <col min="14" max="14" width="15.875" style="523" customWidth="1"/>
     <col min="15" max="15" width="9" style="523"/>
-    <col min="16" max="16" width="14.625" style="776" customWidth="1"/>
+    <col min="16" max="16" width="14.5" style="776" customWidth="1"/>
     <col min="17" max="16384" width="9" style="523"/>
   </cols>
   <sheetData>
@@ -13381,19 +13473,19 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="35.85" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="799" t="s">
+      <c r="A3" s="809" t="s">
         <v>204</v>
       </c>
-      <c r="B3" s="800"/>
-      <c r="C3" s="800"/>
-      <c r="D3" s="800"/>
-      <c r="E3" s="800"/>
-      <c r="F3" s="800"/>
-      <c r="G3" s="800"/>
-      <c r="H3" s="800"/>
-      <c r="I3" s="800"/>
-      <c r="J3" s="800"/>
-      <c r="K3" s="801"/>
+      <c r="B3" s="810"/>
+      <c r="C3" s="810"/>
+      <c r="D3" s="810"/>
+      <c r="E3" s="810"/>
+      <c r="F3" s="810"/>
+      <c r="G3" s="810"/>
+      <c r="H3" s="810"/>
+      <c r="I3" s="810"/>
+      <c r="J3" s="810"/>
+      <c r="K3" s="811"/>
       <c r="L3" s="769" t="s">
         <v>205</v>
       </c>
@@ -13408,18 +13500,18 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A4" s="802" t="s">
+      <c r="A4" s="812" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="802"/>
-      <c r="C4" s="802"/>
-      <c r="D4" s="802"/>
-      <c r="E4" s="802"/>
-      <c r="F4" s="802"/>
-      <c r="G4" s="803" t="s">
+      <c r="B4" s="812"/>
+      <c r="C4" s="812"/>
+      <c r="D4" s="812"/>
+      <c r="E4" s="812"/>
+      <c r="F4" s="812"/>
+      <c r="G4" s="813" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="803" t="s">
+      <c r="H4" s="813" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="622" t="s">
@@ -13434,88 +13526,88 @@
       <c r="L4" s="742" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="806" t="s">
+      <c r="M4" s="816" t="s">
         <v>14</v>
       </c>
       <c r="N4" s="699"/>
-      <c r="P4" s="822" t="s">
+      <c r="P4" s="802" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="813" t="s">
+      <c r="A5" s="805" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="825" t="s">
+      <c r="B5" s="806" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="813" t="s">
+      <c r="C5" s="805" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="813" t="s">
+      <c r="D5" s="805" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="810" t="s">
+      <c r="E5" s="820" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="813" t="s">
+      <c r="F5" s="805" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="804"/>
-      <c r="H5" s="804"/>
+      <c r="G5" s="814"/>
+      <c r="H5" s="814"/>
       <c r="I5" s="623"/>
       <c r="J5" s="671"/>
       <c r="K5" s="671" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="743"/>
-      <c r="M5" s="807"/>
+      <c r="M5" s="817"/>
       <c r="N5" s="700"/>
-      <c r="P5" s="823"/>
+      <c r="P5" s="803"/>
     </row>
     <row r="6" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="813"/>
-      <c r="B6" s="825"/>
-      <c r="C6" s="813"/>
-      <c r="D6" s="813"/>
-      <c r="E6" s="811"/>
-      <c r="F6" s="813"/>
-      <c r="G6" s="804"/>
-      <c r="H6" s="804"/>
-      <c r="I6" s="814" t="s">
+      <c r="A6" s="805"/>
+      <c r="B6" s="806"/>
+      <c r="C6" s="805"/>
+      <c r="D6" s="805"/>
+      <c r="E6" s="821"/>
+      <c r="F6" s="805"/>
+      <c r="G6" s="814"/>
+      <c r="H6" s="814"/>
+      <c r="I6" s="823" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="816" t="s">
+      <c r="J6" s="825" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="818" t="s">
+      <c r="K6" s="827" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="820" t="s">
+      <c r="L6" s="829" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="808" t="s">
+      <c r="M6" s="818" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="826"/>
-      <c r="P6" s="823"/>
+      <c r="N6" s="807"/>
+      <c r="P6" s="803"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A7" s="813"/>
-      <c r="B7" s="825"/>
-      <c r="C7" s="813"/>
-      <c r="D7" s="813"/>
-      <c r="E7" s="812"/>
-      <c r="F7" s="813"/>
-      <c r="G7" s="805"/>
-      <c r="H7" s="805"/>
-      <c r="I7" s="815"/>
-      <c r="J7" s="817"/>
-      <c r="K7" s="819"/>
-      <c r="L7" s="821"/>
-      <c r="M7" s="809"/>
-      <c r="N7" s="827"/>
-      <c r="P7" s="824"/>
+      <c r="A7" s="805"/>
+      <c r="B7" s="806"/>
+      <c r="C7" s="805"/>
+      <c r="D7" s="805"/>
+      <c r="E7" s="822"/>
+      <c r="F7" s="805"/>
+      <c r="G7" s="815"/>
+      <c r="H7" s="815"/>
+      <c r="I7" s="824"/>
+      <c r="J7" s="826"/>
+      <c r="K7" s="828"/>
+      <c r="L7" s="830"/>
+      <c r="M7" s="819"/>
+      <c r="N7" s="808"/>
+      <c r="P7" s="804"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="507">
@@ -13594,7 +13686,7 @@
         <v>45796</v>
       </c>
       <c r="K9" s="673" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L9" s="745">
         <v>45863</v>
@@ -14689,16 +14781,16 @@
       </c>
       <c r="B34" s="661"/>
       <c r="C34" s="412" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="474" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E34" s="474" t="s">
         <v>219</v>
       </c>
       <c r="F34" s="474" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G34" s="632">
         <v>43.756300000000003</v>
@@ -14734,16 +14826,16 @@
       </c>
       <c r="B35" s="663"/>
       <c r="C35" s="411" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D35" s="475" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35" s="475" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F35" s="475" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G35" s="634">
         <v>43.696800000000003</v>
@@ -14778,19 +14870,19 @@
         <v>29</v>
       </c>
       <c r="B36" s="545" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C36" s="414" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D36" s="414" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E36" s="414" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F36" s="414" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G36" s="641">
         <v>44.368572</v>
@@ -14805,7 +14897,7 @@
         <v>45798</v>
       </c>
       <c r="K36" s="688" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L36" s="744">
         <v>45860</v>
@@ -14826,16 +14918,16 @@
         <v>85</v>
       </c>
       <c r="C37" s="474" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D37" s="474" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E37" s="473" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F37" s="474" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G37" s="771">
         <v>44.000500000000002</v>
@@ -14850,7 +14942,7 @@
         <v>45797</v>
       </c>
       <c r="K37" s="686" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L37" s="746">
         <v>45858</v>
@@ -14868,19 +14960,19 @@
         <v>31</v>
       </c>
       <c r="B38" s="545" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C38" s="714" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D38" s="470" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E38" s="470" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F38" s="709" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G38" s="630">
         <v>43.803699999999999</v>
@@ -14895,7 +14987,7 @@
         <v>45790</v>
       </c>
       <c r="K38" s="452" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L38" s="754">
         <v>45853</v>
@@ -14914,16 +15006,16 @@
       </c>
       <c r="B39" s="659"/>
       <c r="C39" s="412" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D39" s="474" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E39" s="474" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F39" s="474" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G39" s="644">
         <v>43.831299999999999</v>
@@ -14938,7 +15030,7 @@
         <v>45794</v>
       </c>
       <c r="K39" s="688" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L39" s="747">
         <v>45853</v>
@@ -14956,19 +15048,19 @@
         <v>33</v>
       </c>
       <c r="B40" s="659" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" s="412" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" s="474" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" s="474" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F40" s="474" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G40" s="632">
         <v>43.392699999999998</v>
@@ -14983,7 +15075,7 @@
         <v>45797</v>
       </c>
       <c r="K40" s="688" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L40" s="747">
         <v>45855</v>
@@ -15002,16 +15094,16 @@
       </c>
       <c r="B41" s="659"/>
       <c r="C41" s="412" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D41" s="474" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E41" s="474" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F41" s="474" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G41" s="632">
         <v>43.430799999999998</v>
@@ -15026,7 +15118,7 @@
         <v>45804</v>
       </c>
       <c r="K41" s="688" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L41" s="747">
         <v>45855</v>
@@ -15045,16 +15137,16 @@
       </c>
       <c r="B42" s="664"/>
       <c r="C42" s="412" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D42" s="474" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E42" s="474" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F42" s="474" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G42" s="632">
         <v>43.703099999999999</v>
@@ -15069,7 +15161,7 @@
         <v>45790</v>
       </c>
       <c r="K42" s="456" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L42" s="747">
         <v>45853</v>
@@ -15088,16 +15180,16 @@
       </c>
       <c r="B43" s="659"/>
       <c r="C43" s="412" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D43" s="474" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E43" s="474" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F43" s="474" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G43" s="632">
         <v>43.6995</v>
@@ -15112,7 +15204,7 @@
         <v>45792</v>
       </c>
       <c r="K43" s="456" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L43" s="747">
         <v>45853</v>
@@ -15131,16 +15223,16 @@
       </c>
       <c r="B44" s="659"/>
       <c r="C44" s="412" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D44" s="474" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" s="474" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F44" s="474" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G44" s="632">
         <v>43.841327999999997</v>
@@ -15155,7 +15247,7 @@
         <v>45792</v>
       </c>
       <c r="K44" s="456" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L44" s="747">
         <v>45850</v>
@@ -15198,7 +15290,7 @@
         <v>45798</v>
       </c>
       <c r="K45" s="456" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L45" s="755">
         <v>45855</v>
@@ -15284,7 +15376,7 @@
         <v>45796</v>
       </c>
       <c r="K47" s="686" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L47" s="756">
         <v>45848</v>
@@ -15397,11 +15489,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="P4:P7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:G7"/>
@@ -15415,6 +15502,11 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
+    <mergeCell ref="P4:P7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -15430,65 +15522,65 @@
   <dimension ref="A1:N47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.375" style="523" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="523" customWidth="1"/>
     <col min="2" max="2" width="9" style="523"/>
-    <col min="3" max="4" width="13.375" style="523" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="523" customWidth="1"/>
-    <col min="6" max="6" width="24.375" style="523" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="523" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="523" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.375" style="28" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="523" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="523" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="523" customWidth="1"/>
+    <col min="6" max="6" width="24.5" style="523" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5" style="28" customWidth="1"/>
+    <col min="14" max="14" width="19.5" style="523" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="523"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.15">
       <c r="A1" s="517" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L1" s="693">
         <v>45435</v>
       </c>
       <c r="M1" s="693" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="21" x14ac:dyDescent="0.15">
       <c r="A2" s="517" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="828" t="s">
-        <v>226</v>
-      </c>
-      <c r="H2" s="800"/>
-      <c r="I2" s="800"/>
-      <c r="J2" s="800"/>
-      <c r="K2" s="801"/>
-      <c r="L2" s="828" t="s">
+      <c r="G2" s="833" t="s">
         <v>227</v>
       </c>
-      <c r="M2" s="800"/>
+      <c r="H2" s="810"/>
+      <c r="I2" s="810"/>
+      <c r="J2" s="810"/>
+      <c r="K2" s="811"/>
+      <c r="L2" s="833" t="s">
+        <v>228</v>
+      </c>
+      <c r="M2" s="810"/>
       <c r="N2" s="698" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A3" s="802" t="s">
-        <v>228</v>
-      </c>
-      <c r="B3" s="802"/>
-      <c r="C3" s="802"/>
-      <c r="D3" s="802"/>
-      <c r="E3" s="802"/>
-      <c r="F3" s="802"/>
-      <c r="G3" s="803" t="s">
+      <c r="A3" s="812" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="812"/>
+      <c r="C3" s="812"/>
+      <c r="D3" s="812"/>
+      <c r="E3" s="812"/>
+      <c r="F3" s="812"/>
+      <c r="G3" s="813" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="803" t="s">
+      <c r="H3" s="813" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="622" t="s">
@@ -15503,82 +15595,82 @@
       <c r="L3" s="649" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="829" t="s">
+      <c r="M3" s="834" t="s">
         <v>14</v>
       </c>
       <c r="N3" s="699"/>
     </row>
     <row r="4" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="813" t="s">
+      <c r="A4" s="805" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="825" t="s">
+      <c r="B4" s="806" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="813" t="s">
+      <c r="C4" s="805" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="813" t="s">
+      <c r="D4" s="805" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="810" t="s">
+      <c r="E4" s="820" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="813" t="s">
+      <c r="F4" s="805" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="804"/>
-      <c r="H4" s="804"/>
+      <c r="G4" s="814"/>
+      <c r="H4" s="814"/>
       <c r="I4" s="623"/>
       <c r="J4" s="671"/>
       <c r="K4" s="671" t="s">
         <v>22</v>
       </c>
       <c r="L4" s="650"/>
-      <c r="M4" s="830"/>
+      <c r="M4" s="835"/>
       <c r="N4" s="700"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="813"/>
-      <c r="B5" s="825"/>
-      <c r="C5" s="813"/>
-      <c r="D5" s="813"/>
-      <c r="E5" s="811"/>
-      <c r="F5" s="813"/>
-      <c r="G5" s="804"/>
-      <c r="H5" s="804"/>
-      <c r="I5" s="814" t="s">
+      <c r="A5" s="805"/>
+      <c r="B5" s="806"/>
+      <c r="C5" s="805"/>
+      <c r="D5" s="805"/>
+      <c r="E5" s="821"/>
+      <c r="F5" s="805"/>
+      <c r="G5" s="814"/>
+      <c r="H5" s="814"/>
+      <c r="I5" s="823" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="816" t="s">
+      <c r="J5" s="825" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="818" t="s">
+      <c r="K5" s="827" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="833" t="s">
+      <c r="L5" s="831" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="831" t="s">
+      <c r="M5" s="836" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="826"/>
+      <c r="N5" s="807"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A6" s="813"/>
-      <c r="B6" s="825"/>
-      <c r="C6" s="813"/>
-      <c r="D6" s="813"/>
-      <c r="E6" s="812"/>
-      <c r="F6" s="813"/>
-      <c r="G6" s="805"/>
-      <c r="H6" s="805"/>
-      <c r="I6" s="815"/>
-      <c r="J6" s="817"/>
-      <c r="K6" s="819"/>
-      <c r="L6" s="834"/>
-      <c r="M6" s="832"/>
-      <c r="N6" s="827"/>
+      <c r="A6" s="805"/>
+      <c r="B6" s="806"/>
+      <c r="C6" s="805"/>
+      <c r="D6" s="805"/>
+      <c r="E6" s="822"/>
+      <c r="F6" s="805"/>
+      <c r="G6" s="815"/>
+      <c r="H6" s="815"/>
+      <c r="I6" s="824"/>
+      <c r="J6" s="826"/>
+      <c r="K6" s="828"/>
+      <c r="L6" s="832"/>
+      <c r="M6" s="837"/>
+      <c r="N6" s="808"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A7" s="507">
@@ -15630,7 +15722,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="412" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D8" s="412" t="s">
         <v>34</v>
@@ -15639,7 +15731,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="412" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G8" s="712">
         <v>42.488999999999997</v>
@@ -15654,7 +15746,7 @@
         <v>45427</v>
       </c>
       <c r="K8" s="673" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L8" s="652">
         <v>45496</v>
@@ -15663,7 +15755,7 @@
         <v>8.5</v>
       </c>
       <c r="N8" s="711" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.15">
@@ -15705,7 +15797,7 @@
         <v>6.1</v>
       </c>
       <c r="N9" s="703" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.15">
@@ -15986,7 +16078,7 @@
         <v>45432</v>
       </c>
       <c r="K16" s="497" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L16" s="665">
         <v>45493</v>
@@ -16066,7 +16158,7 @@
         <v>45435</v>
       </c>
       <c r="K18" s="680" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L18" s="668">
         <v>45501</v>
@@ -16117,7 +16209,7 @@
         <v>7.3</v>
       </c>
       <c r="N19" s="701" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.15">
@@ -16161,7 +16253,7 @@
         <v>7.1</v>
       </c>
       <c r="N20" s="702" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.15">
@@ -16327,7 +16419,7 @@
         <v>7</v>
       </c>
       <c r="N24" s="731" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.15">
@@ -16369,7 +16461,7 @@
         <v>6.9</v>
       </c>
       <c r="N25" s="732" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.15">
@@ -16547,7 +16639,7 @@
         <v>129</v>
       </c>
       <c r="F30" s="474" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G30" s="638">
         <v>43.453600000000002</v>
@@ -16651,7 +16743,7 @@
         <v>6.6</v>
       </c>
       <c r="N32" s="711" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.15">
@@ -16660,16 +16752,16 @@
       </c>
       <c r="B33" s="661"/>
       <c r="C33" s="474" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D33" s="474" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E33" s="474" t="s">
         <v>219</v>
       </c>
       <c r="F33" s="474" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G33" s="638">
         <v>43.756300000000003</v>
@@ -16700,16 +16792,16 @@
       </c>
       <c r="B34" s="663"/>
       <c r="C34" s="475" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="475" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" s="475" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F34" s="475" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G34" s="639">
         <v>43.696800000000003</v>
@@ -16739,19 +16831,19 @@
         <v>29</v>
       </c>
       <c r="B35" s="545" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" s="414" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D35" s="414" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E35" s="414" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F35" s="414" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G35" s="713">
         <v>44.368572</v>
@@ -16766,7 +16858,7 @@
         <v>45432</v>
       </c>
       <c r="K35" s="688" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L35" s="651">
         <v>45498</v>
@@ -16775,7 +16867,7 @@
         <v>7.6</v>
       </c>
       <c r="N35" s="690" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.15">
@@ -16786,16 +16878,16 @@
         <v>85</v>
       </c>
       <c r="C36" s="474" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D36" s="474" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" s="473" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F36" s="474" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G36" s="643">
         <v>44.000500000000002</v>
@@ -16810,7 +16902,7 @@
         <v>45431</v>
       </c>
       <c r="K36" s="686" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L36" s="653">
         <v>45495</v>
@@ -16825,19 +16917,19 @@
         <v>31</v>
       </c>
       <c r="B37" s="545" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C37" s="714" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D37" s="470" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37" s="470" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F37" s="709" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G37" s="636">
         <v>43.803699999999999</v>
@@ -16852,7 +16944,7 @@
         <v>45424</v>
       </c>
       <c r="K37" s="452" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L37" s="669">
         <v>45495</v>
@@ -16868,16 +16960,16 @@
       </c>
       <c r="B38" s="659"/>
       <c r="C38" s="412" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D38" s="474" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="474" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F38" s="474" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G38" s="644">
         <v>43.831299999999999</v>
@@ -16892,7 +16984,7 @@
         <v>45428</v>
       </c>
       <c r="K38" s="688" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L38" s="665">
         <v>45493</v>
@@ -16907,19 +16999,19 @@
         <v>33</v>
       </c>
       <c r="B39" s="659" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C39" s="412" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D39" s="474" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E39" s="474" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F39" s="474" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G39" s="638">
         <v>43.392699999999998</v>
@@ -16934,7 +17026,7 @@
         <v>45429</v>
       </c>
       <c r="K39" s="688" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L39" s="665">
         <v>45495</v>
@@ -16950,16 +17042,16 @@
       </c>
       <c r="B40" s="659"/>
       <c r="C40" s="412" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" s="474" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E40" s="474" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F40" s="474" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G40" s="638">
         <v>43.430799999999998</v>
@@ -16974,7 +17066,7 @@
         <v>45440</v>
       </c>
       <c r="K40" s="688" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L40" s="665">
         <v>45495</v>
@@ -16990,16 +17082,16 @@
       </c>
       <c r="B41" s="664"/>
       <c r="C41" s="412" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D41" s="474" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E41" s="474" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F41" s="474" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G41" s="638">
         <v>43.703099999999999</v>
@@ -17014,7 +17106,7 @@
         <v>45427</v>
       </c>
       <c r="K41" s="456" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L41" s="665">
         <v>45492</v>
@@ -17030,16 +17122,16 @@
       </c>
       <c r="B42" s="659"/>
       <c r="C42" s="412" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D42" s="474" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42" s="474" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F42" s="474" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G42" s="638">
         <v>43.6995</v>
@@ -17054,7 +17146,7 @@
         <v>45433</v>
       </c>
       <c r="K42" s="456" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L42" s="665">
         <v>45499</v>
@@ -17070,16 +17162,16 @@
       </c>
       <c r="B43" s="659"/>
       <c r="C43" s="412" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D43" s="474" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" s="474" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F43" s="474" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G43" s="638">
         <v>43.851399999999998</v>
@@ -17094,7 +17186,7 @@
         <v>45427</v>
       </c>
       <c r="K43" s="456" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L43" s="665">
         <v>45496</v>
@@ -17134,7 +17226,7 @@
         <v>45426</v>
       </c>
       <c r="K44" s="456" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L44" s="656">
         <v>45495</v>
@@ -17183,7 +17275,7 @@
         <v>7.9</v>
       </c>
       <c r="N45" s="707" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.15">
@@ -17216,7 +17308,7 @@
         <v>45430</v>
       </c>
       <c r="K46" s="686" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L46" s="657">
         <v>45493</v>
@@ -17228,20 +17320,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A47" s="524" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B47" s="533"/>
       <c r="L47" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="A3:F3"/>
@@ -17253,6 +17338,13 @@
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -17268,48 +17360,48 @@
   <dimension ref="A1:M47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.375" style="523" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="523" customWidth="1"/>
     <col min="2" max="2" width="9" style="523"/>
-    <col min="3" max="4" width="13.375" style="523" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="523" customWidth="1"/>
-    <col min="6" max="6" width="24.375" style="523" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="523" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="523" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="523" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="523" customWidth="1"/>
+    <col min="6" max="6" width="24.5" style="523" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="523" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="523"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.15">
       <c r="A1" s="517" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="21" x14ac:dyDescent="0.15">
       <c r="A2" s="517" t="s">
-        <v>243</v>
-      </c>
-      <c r="K2" s="835">
+        <v>244</v>
+      </c>
+      <c r="K2" s="838">
         <f ca="1">NOW()</f>
-        <v>46206.598910995373</v>
-      </c>
-      <c r="L2" s="835"/>
+        <v>46246.77676990741</v>
+      </c>
+      <c r="L2" s="838"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A3" s="802" t="s">
-        <v>244</v>
-      </c>
-      <c r="B3" s="802"/>
-      <c r="C3" s="802"/>
-      <c r="D3" s="802"/>
-      <c r="E3" s="802"/>
-      <c r="F3" s="802"/>
-      <c r="G3" s="836" t="s">
+      <c r="A3" s="812" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="812"/>
+      <c r="C3" s="812"/>
+      <c r="D3" s="812"/>
+      <c r="E3" s="812"/>
+      <c r="F3" s="812"/>
+      <c r="G3" s="839" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="836" t="s">
+      <c r="H3" s="839" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="426" t="s">
@@ -17326,26 +17418,26 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="813" t="s">
+      <c r="A4" s="805" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="825" t="s">
+      <c r="B4" s="806" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="813" t="s">
+      <c r="C4" s="805" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="813" t="s">
+      <c r="D4" s="805" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="810" t="s">
+      <c r="E4" s="820" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="813" t="s">
+      <c r="F4" s="805" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="837"/>
-      <c r="H4" s="837"/>
+      <c r="G4" s="840"/>
+      <c r="H4" s="840"/>
       <c r="I4" s="427"/>
       <c r="J4" s="291"/>
       <c r="K4" s="291" t="s">
@@ -17354,40 +17446,40 @@
       <c r="L4" s="420"/>
     </row>
     <row r="5" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="813"/>
-      <c r="B5" s="825"/>
-      <c r="C5" s="813"/>
-      <c r="D5" s="813"/>
-      <c r="E5" s="811"/>
-      <c r="F5" s="813"/>
-      <c r="G5" s="837"/>
-      <c r="H5" s="837"/>
-      <c r="I5" s="839" t="s">
+      <c r="A5" s="805"/>
+      <c r="B5" s="806"/>
+      <c r="C5" s="805"/>
+      <c r="D5" s="805"/>
+      <c r="E5" s="821"/>
+      <c r="F5" s="805"/>
+      <c r="G5" s="840"/>
+      <c r="H5" s="840"/>
+      <c r="I5" s="842" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="841" t="s">
+      <c r="J5" s="844" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="843" t="s">
+      <c r="K5" s="846" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="845" t="s">
+      <c r="L5" s="848" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A6" s="813"/>
-      <c r="B6" s="825"/>
-      <c r="C6" s="813"/>
-      <c r="D6" s="813"/>
-      <c r="E6" s="812"/>
-      <c r="F6" s="813"/>
-      <c r="G6" s="838"/>
-      <c r="H6" s="838"/>
-      <c r="I6" s="840"/>
-      <c r="J6" s="842"/>
-      <c r="K6" s="844"/>
-      <c r="L6" s="846"/>
+      <c r="A6" s="805"/>
+      <c r="B6" s="806"/>
+      <c r="C6" s="805"/>
+      <c r="D6" s="805"/>
+      <c r="E6" s="822"/>
+      <c r="F6" s="805"/>
+      <c r="G6" s="841"/>
+      <c r="H6" s="841"/>
+      <c r="I6" s="843"/>
+      <c r="J6" s="845"/>
+      <c r="K6" s="847"/>
+      <c r="L6" s="849"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7" s="507">
@@ -17421,7 +17513,7 @@
         <v>45073</v>
       </c>
       <c r="K7" s="434" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L7" s="549">
         <v>45132</v>
@@ -17435,16 +17527,16 @@
         <v>32</v>
       </c>
       <c r="C8" s="412" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D8" s="412" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="412" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F8" s="412" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G8" s="589">
         <v>42.429499999999997</v>
@@ -17459,7 +17551,7 @@
         <v>45071</v>
       </c>
       <c r="K8" s="435" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L8" s="555">
         <v>45129</v>
@@ -17495,7 +17587,7 @@
         <v>45069</v>
       </c>
       <c r="K9" s="436" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L9" s="578">
         <v>45135</v>
@@ -17533,7 +17625,7 @@
         <v>45067</v>
       </c>
       <c r="K10" s="145" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L10" s="555">
         <v>45129</v>
@@ -17571,7 +17663,7 @@
         <v>45064</v>
       </c>
       <c r="K11" s="144" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L11" s="555">
         <v>45127</v>
@@ -17607,7 +17699,7 @@
         <v>45065</v>
       </c>
       <c r="K12" s="146" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L12" s="578">
         <v>45127</v>
@@ -17645,7 +17737,7 @@
         <v>44698</v>
       </c>
       <c r="K13" s="145" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L13" s="549">
         <v>45129</v>
@@ -17683,7 +17775,7 @@
         <v>45069</v>
       </c>
       <c r="K14" s="273" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L14" s="690">
         <v>45135</v>
@@ -17719,7 +17811,7 @@
         <v>44701</v>
       </c>
       <c r="K15" s="144" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L15" s="555">
         <v>45134</v>
@@ -17755,7 +17847,7 @@
         <v>45069</v>
       </c>
       <c r="K16" s="144" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L16" s="555">
         <v>45128</v>
@@ -17791,7 +17883,7 @@
         <v>45065</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L17" s="555">
         <v>45130</v>
@@ -17827,7 +17919,7 @@
         <v>44703</v>
       </c>
       <c r="K18" s="146" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L18" s="572">
         <v>45134</v>
@@ -17865,7 +17957,7 @@
         <v>45067</v>
       </c>
       <c r="K19" s="548" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L19" s="549">
         <v>45127</v>
@@ -17903,7 +17995,7 @@
         <v>45071</v>
       </c>
       <c r="K20" s="554" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L20" s="555">
         <v>45133</v>
@@ -17941,7 +18033,7 @@
         <v>45066</v>
       </c>
       <c r="K21" s="560" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L21" s="549">
         <v>45131</v>
@@ -17977,7 +18069,7 @@
         <v>45062</v>
       </c>
       <c r="K22" s="616" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L22" s="555">
         <v>45126</v>
@@ -18015,7 +18107,7 @@
         <v>44703</v>
       </c>
       <c r="K23" s="565" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L23" s="555">
         <v>45127</v>
@@ -18051,7 +18143,7 @@
         <v>44700</v>
       </c>
       <c r="K24" s="565" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L24" s="555">
         <v>45125</v>
@@ -18067,13 +18159,13 @@
         <v>106</v>
       </c>
       <c r="D25" s="563" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E25" s="575" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F25" s="563" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G25" s="599">
         <v>43.063000000000002</v>
@@ -18088,7 +18180,7 @@
         <v>44701</v>
       </c>
       <c r="K25" s="565" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L25" s="555">
         <v>45129</v>
@@ -18124,7 +18216,7 @@
         <v>45068</v>
       </c>
       <c r="K26" s="565" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L26" s="566">
         <v>45130</v>
@@ -18160,7 +18252,7 @@
         <v>45070</v>
       </c>
       <c r="K27" s="619" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L27" s="555">
         <v>45132</v>
@@ -18196,7 +18288,7 @@
         <v>45071</v>
       </c>
       <c r="K28" s="565" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L28" s="555">
         <v>45131</v>
@@ -18232,7 +18324,7 @@
         <v>45065</v>
       </c>
       <c r="K29" s="567" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L29" s="555">
         <v>45132</v>
@@ -18253,7 +18345,7 @@
         <v>129</v>
       </c>
       <c r="F30" s="563" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G30" s="599">
         <v>43.453600000000002</v>
@@ -18268,7 +18360,7 @@
         <v>45073</v>
       </c>
       <c r="K30" s="565" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L30" s="555">
         <v>45127</v>
@@ -18304,7 +18396,7 @@
         <v>44698</v>
       </c>
       <c r="K31" s="565" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L31" s="555">
         <v>45131</v>
@@ -18340,7 +18432,7 @@
         <v>44698</v>
       </c>
       <c r="K32" s="565" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L32" s="555">
         <v>45124</v>
@@ -18352,16 +18444,16 @@
       </c>
       <c r="B33" s="562"/>
       <c r="C33" s="563" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D33" s="563" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E33" s="575" t="s">
         <v>219</v>
       </c>
       <c r="F33" s="563" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G33" s="599">
         <v>43.756300000000003</v>
@@ -18376,7 +18468,7 @@
         <v>45067</v>
       </c>
       <c r="K33" s="565" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L33" s="555">
         <v>45131</v>
@@ -18388,16 +18480,16 @@
       </c>
       <c r="B34" s="512"/>
       <c r="C34" s="569" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="569" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" s="475" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F34" s="569" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G34" s="601">
         <v>43.696800000000003</v>
@@ -18412,7 +18504,7 @@
         <v>44703</v>
       </c>
       <c r="K34" s="571" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L34" s="572">
         <v>45132</v>
@@ -18423,19 +18515,19 @@
         <v>29</v>
       </c>
       <c r="B35" s="545" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" s="414" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D35" s="558" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E35" s="414" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F35" s="558" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G35" s="602">
         <v>43.365699999999997</v>
@@ -18450,7 +18542,7 @@
         <v>45065</v>
       </c>
       <c r="K35" s="574" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L35" s="549">
         <v>45132</v>
@@ -18464,16 +18556,16 @@
         <v>85</v>
       </c>
       <c r="C36" s="474" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D36" s="474" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" s="473" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F36" s="563" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G36" s="603">
         <v>44.000500000000002</v>
@@ -18488,7 +18580,7 @@
         <v>45064</v>
       </c>
       <c r="K36" s="577" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L36" s="578">
         <v>45129</v>
@@ -18499,19 +18591,19 @@
         <v>31</v>
       </c>
       <c r="B37" s="557" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C37" s="470" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D37" s="470" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37" s="470" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F37" s="579" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G37" s="602">
         <v>43.803699999999999</v>
@@ -18526,7 +18618,7 @@
         <v>45061</v>
       </c>
       <c r="K37" s="581" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L37" s="691">
         <v>45128</v>
@@ -18538,16 +18630,16 @@
       </c>
       <c r="B38" s="551"/>
       <c r="C38" s="474" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D38" s="474" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="474" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F38" s="474" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G38" s="604">
         <v>43.831299999999999</v>
@@ -18562,7 +18654,7 @@
         <v>45065</v>
       </c>
       <c r="K38" s="583" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L38" s="555">
         <v>45128</v>
@@ -18573,19 +18665,19 @@
         <v>33</v>
       </c>
       <c r="B39" s="551" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C39" s="474" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D39" s="474" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E39" s="474" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F39" s="563" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G39" s="599">
         <v>43.392699999999998</v>
@@ -18600,7 +18692,7 @@
         <v>44699</v>
       </c>
       <c r="K39" s="583" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L39" s="555">
         <v>45133</v>
@@ -18612,16 +18704,16 @@
       </c>
       <c r="B40" s="551"/>
       <c r="C40" s="474" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" s="474" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E40" s="474" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F40" s="474" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G40" s="599">
         <v>43.430799999999998</v>
@@ -18636,7 +18728,7 @@
         <v>45075</v>
       </c>
       <c r="K40" s="583" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L40" s="555">
         <v>45133</v>
@@ -18648,16 +18740,16 @@
       </c>
       <c r="B41" s="585"/>
       <c r="C41" s="474" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D41" s="474" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E41" s="474" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F41" s="563" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G41" s="599">
         <v>43.703099999999999</v>
@@ -18672,7 +18764,7 @@
         <v>45063</v>
       </c>
       <c r="K41" s="586" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L41" s="555">
         <v>45130</v>
@@ -18684,16 +18776,16 @@
       </c>
       <c r="B42" s="551"/>
       <c r="C42" s="474" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D42" s="474" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42" s="474" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F42" s="563" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G42" s="599">
         <v>43.6995</v>
@@ -18708,7 +18800,7 @@
         <v>45063</v>
       </c>
       <c r="K42" s="586" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L42" s="555">
         <v>45129</v>
@@ -18720,16 +18812,16 @@
       </c>
       <c r="B43" s="551"/>
       <c r="C43" s="474" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D43" s="474" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" s="474" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F43" s="563" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G43" s="599">
         <v>43.851399999999998</v>
@@ -18744,7 +18836,7 @@
         <v>45061</v>
       </c>
       <c r="K43" s="586" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L43" s="555">
         <v>45129</v>
@@ -18780,7 +18872,7 @@
         <v>45060</v>
       </c>
       <c r="K44" s="586" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="L44" s="584">
         <v>45129</v>
@@ -18816,7 +18908,7 @@
         <v>45072</v>
       </c>
       <c r="K45" s="586" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L45" s="584">
         <v>45131</v>
@@ -18852,7 +18944,7 @@
         <v>44700</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L46" s="692">
         <v>45131</v>
@@ -18860,7 +18952,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A47" s="524" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B47" s="533"/>
       <c r="L47" s="12"/>
@@ -18897,50 +18989,50 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="523"/>
-    <col min="3" max="4" width="13.375" style="523" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="523" customWidth="1"/>
     <col min="5" max="5" width="18" style="523" customWidth="1"/>
-    <col min="6" max="6" width="24.375" style="523" customWidth="1"/>
-    <col min="7" max="7" width="11.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="9.375" style="28" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="23.375" style="28" customWidth="1"/>
-    <col min="14" max="14" width="2.375" style="28" customWidth="1"/>
-    <col min="15" max="15" width="9.375" style="28" customWidth="1"/>
-    <col min="16" max="17" width="10.375" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.375" style="28" customWidth="1"/>
-    <col min="19" max="19" width="24.375" style="523" customWidth="1"/>
+    <col min="6" max="6" width="24.5" style="523" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" style="28" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="23.5" style="28" customWidth="1"/>
+    <col min="14" max="14" width="2.5" style="28" customWidth="1"/>
+    <col min="15" max="15" width="9.5" style="28" customWidth="1"/>
+    <col min="16" max="17" width="10.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5" style="28" customWidth="1"/>
+    <col min="19" max="19" width="24.5" style="523" customWidth="1"/>
     <col min="20" max="16384" width="9" style="523"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.15">
       <c r="A1" s="517" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S1" s="524" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="21" x14ac:dyDescent="0.15">
       <c r="A2" s="517" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="S2" s="525">
         <f ca="1">NOW()</f>
-        <v>46206.598910995373</v>
+        <v>46246.77676990741</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="27" x14ac:dyDescent="0.15">
-      <c r="A3" s="802" t="s">
-        <v>259</v>
-      </c>
-      <c r="B3" s="802"/>
-      <c r="C3" s="802"/>
-      <c r="D3" s="802"/>
-      <c r="E3" s="802"/>
-      <c r="F3" s="802"/>
+      <c r="A3" s="812" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="812"/>
+      <c r="C3" s="812"/>
+      <c r="D3" s="812"/>
+      <c r="E3" s="812"/>
+      <c r="F3" s="812"/>
       <c r="G3" s="426" t="s">
         <v>10</v>
       </c>
@@ -18954,42 +19046,42 @@
         <v>13</v>
       </c>
       <c r="K3" s="410" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L3" s="430" t="s">
-        <v>261</v>
-      </c>
-      <c r="M3" s="859" t="s">
+        <v>262</v>
+      </c>
+      <c r="M3" s="857" t="s">
         <v>5</v>
       </c>
       <c r="N3" s="438"/>
-      <c r="O3" s="853" t="s">
-        <v>262</v>
-      </c>
-      <c r="P3" s="854"/>
-      <c r="Q3" s="854"/>
-      <c r="R3" s="855"/>
-      <c r="S3" s="856" t="s">
+      <c r="O3" s="851" t="s">
+        <v>263</v>
+      </c>
+      <c r="P3" s="852"/>
+      <c r="Q3" s="852"/>
+      <c r="R3" s="853"/>
+      <c r="S3" s="854" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="813" t="s">
+      <c r="A4" s="805" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="825" t="s">
+      <c r="B4" s="806" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="813" t="s">
+      <c r="C4" s="805" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="813" t="s">
+      <c r="D4" s="805" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="810" t="s">
+      <c r="E4" s="820" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="813" t="s">
+      <c r="F4" s="805" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="427"/>
@@ -19000,73 +19092,73 @@
       <c r="J4" s="387"/>
       <c r="K4" s="409"/>
       <c r="L4" s="526"/>
-      <c r="M4" s="847"/>
+      <c r="M4" s="858"/>
       <c r="N4" s="524"/>
-      <c r="O4" s="802" t="s">
-        <v>263</v>
-      </c>
-      <c r="P4" s="851" t="s">
+      <c r="O4" s="812" t="s">
         <v>264</v>
       </c>
-      <c r="Q4" s="859" t="s">
+      <c r="P4" s="862" t="s">
         <v>265</v>
       </c>
-      <c r="R4" s="851" t="s">
+      <c r="Q4" s="857" t="s">
         <v>266</v>
       </c>
-      <c r="S4" s="857"/>
+      <c r="R4" s="862" t="s">
+        <v>267</v>
+      </c>
+      <c r="S4" s="855"/>
     </row>
     <row r="5" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="813"/>
-      <c r="B5" s="825"/>
-      <c r="C5" s="813"/>
-      <c r="D5" s="813"/>
-      <c r="E5" s="811"/>
-      <c r="F5" s="813"/>
-      <c r="G5" s="839" t="s">
+      <c r="A5" s="805"/>
+      <c r="B5" s="806"/>
+      <c r="C5" s="805"/>
+      <c r="D5" s="805"/>
+      <c r="E5" s="821"/>
+      <c r="F5" s="805"/>
+      <c r="G5" s="842" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="841" t="s">
+      <c r="H5" s="844" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="843" t="s">
+      <c r="I5" s="846" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="845" t="s">
+      <c r="J5" s="848" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="847"/>
-      <c r="L5" s="849" t="s">
-        <v>267</v>
-      </c>
-      <c r="M5" s="849"/>
+      <c r="K5" s="858"/>
+      <c r="L5" s="860" t="s">
+        <v>268</v>
+      </c>
+      <c r="M5" s="860"/>
       <c r="N5" s="439"/>
-      <c r="O5" s="802"/>
-      <c r="P5" s="851"/>
-      <c r="Q5" s="847"/>
-      <c r="R5" s="851"/>
-      <c r="S5" s="857"/>
+      <c r="O5" s="812"/>
+      <c r="P5" s="862"/>
+      <c r="Q5" s="858"/>
+      <c r="R5" s="862"/>
+      <c r="S5" s="855"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.15">
-      <c r="A6" s="813"/>
-      <c r="B6" s="825"/>
-      <c r="C6" s="813"/>
-      <c r="D6" s="813"/>
-      <c r="E6" s="812"/>
-      <c r="F6" s="813"/>
-      <c r="G6" s="840"/>
-      <c r="H6" s="842"/>
-      <c r="I6" s="844"/>
-      <c r="J6" s="846"/>
-      <c r="K6" s="848"/>
-      <c r="L6" s="850"/>
-      <c r="M6" s="850"/>
+      <c r="A6" s="805"/>
+      <c r="B6" s="806"/>
+      <c r="C6" s="805"/>
+      <c r="D6" s="805"/>
+      <c r="E6" s="822"/>
+      <c r="F6" s="805"/>
+      <c r="G6" s="843"/>
+      <c r="H6" s="845"/>
+      <c r="I6" s="847"/>
+      <c r="J6" s="849"/>
+      <c r="K6" s="859"/>
+      <c r="L6" s="861"/>
+      <c r="M6" s="861"/>
       <c r="N6" s="442"/>
-      <c r="O6" s="802"/>
-      <c r="P6" s="851"/>
-      <c r="Q6" s="848"/>
-      <c r="R6" s="851"/>
-      <c r="S6" s="858"/>
+      <c r="O6" s="812"/>
+      <c r="P6" s="862"/>
+      <c r="Q6" s="859"/>
+      <c r="R6" s="862"/>
+      <c r="S6" s="856"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A7" s="507">
@@ -19094,7 +19186,7 @@
         <v>44702</v>
       </c>
       <c r="I7" s="434" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J7" s="278">
         <v>44772</v>
@@ -19110,7 +19202,7 @@
       <c r="P7" s="470"/>
       <c r="Q7" s="470"/>
       <c r="R7" s="498" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S7" s="467"/>
     </row>
@@ -19122,16 +19214,16 @@
         <v>32</v>
       </c>
       <c r="C8" s="412" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D8" s="412" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="412" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F8" s="412" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G8" s="429">
         <v>44674</v>
@@ -19140,7 +19232,7 @@
         <v>44706</v>
       </c>
       <c r="I8" s="435" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J8" s="279">
         <v>44771</v>
@@ -19156,7 +19248,7 @@
       <c r="P8" s="471"/>
       <c r="Q8" s="471"/>
       <c r="R8" s="478" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S8" s="424"/>
     </row>
@@ -19178,13 +19270,13 @@
         <v>40</v>
       </c>
       <c r="G9" s="535" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H9" s="118">
         <v>44706</v>
       </c>
       <c r="I9" s="436" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J9" s="283">
         <v>44770</v>
@@ -19210,7 +19302,7 @@
         <v>23.310023310023311</v>
       </c>
       <c r="S9" s="424" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.15">
@@ -19239,7 +19331,7 @@
         <v>44703</v>
       </c>
       <c r="I10" s="145" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J10" s="275">
         <v>44767</v>
@@ -19255,8 +19347,8 @@
       <c r="P10" s="471"/>
       <c r="Q10" s="471"/>
       <c r="R10" s="471"/>
-      <c r="S10" s="852" t="s">
-        <v>272</v>
+      <c r="S10" s="850" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.15">
@@ -19285,7 +19377,7 @@
         <v>44698</v>
       </c>
       <c r="I11" s="144" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J11" s="275">
         <v>44767</v>
@@ -19301,7 +19393,7 @@
       <c r="P11" s="471"/>
       <c r="Q11" s="471"/>
       <c r="R11" s="471"/>
-      <c r="S11" s="852"/>
+      <c r="S11" s="850"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A12" s="528">
@@ -19327,7 +19419,7 @@
         <v>44701</v>
       </c>
       <c r="I12" s="146" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J12" s="276">
         <v>44768</v>
@@ -19371,7 +19463,7 @@
         <v>44698</v>
       </c>
       <c r="I13" s="145" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J13" s="274">
         <v>44769</v>
@@ -19397,16 +19489,16 @@
         <v>60</v>
       </c>
       <c r="C14" s="503" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D14" s="503" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E14" s="506" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F14" s="503" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G14" s="110">
         <v>44674</v>
@@ -19415,7 +19507,7 @@
         <v>44703</v>
       </c>
       <c r="I14" s="273" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J14" s="275">
         <v>44774</v>
@@ -19457,7 +19549,7 @@
         <v>44701</v>
       </c>
       <c r="I15" s="273" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J15" s="275">
         <v>44776</v>
@@ -19487,7 +19579,7 @@
         <v>68</v>
       </c>
       <c r="E16" s="503" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F16" s="503" t="s">
         <v>70</v>
@@ -19499,7 +19591,7 @@
         <v>44702</v>
       </c>
       <c r="I16" s="144" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J16" s="275">
         <v>44769</v>
@@ -19529,7 +19621,7 @@
         <v>72</v>
       </c>
       <c r="E17" s="503" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F17" s="503" t="s">
         <v>74</v>
@@ -19541,7 +19633,7 @@
         <v>44702</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J17" s="275">
         <v>44769</v>
@@ -19583,7 +19675,7 @@
         <v>44703</v>
       </c>
       <c r="I18" s="146" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J18" s="277">
         <v>44767</v>
@@ -19627,7 +19719,7 @@
         <v>44703</v>
       </c>
       <c r="I19" s="492" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J19" s="278">
         <v>44769</v>
@@ -19659,7 +19751,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="514" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C20" s="468" t="s">
         <v>86</v>
@@ -19668,7 +19760,7 @@
         <v>87</v>
       </c>
       <c r="E20" s="468" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F20" s="468" t="s">
         <v>89</v>
@@ -19680,7 +19772,7 @@
         <v>44704</v>
       </c>
       <c r="I20" s="497" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J20" s="279">
         <v>44768</v>
@@ -19713,16 +19805,16 @@
       </c>
       <c r="B21" s="514"/>
       <c r="C21" s="530" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D21" s="530" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E21" s="530" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F21" s="530" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G21" s="418">
         <v>44672</v>
@@ -19731,7 +19823,7 @@
         <v>44702</v>
       </c>
       <c r="I21" s="273" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J21" s="522">
         <v>44775</v>
@@ -19755,16 +19847,16 @@
       </c>
       <c r="B22" s="514"/>
       <c r="C22" s="531" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D22" s="531" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E22" s="531" t="s">
+        <v>286</v>
+      </c>
+      <c r="F22" s="531" t="s">
         <v>285</v>
-      </c>
-      <c r="F22" s="531" t="s">
-        <v>284</v>
       </c>
       <c r="G22" s="418">
         <v>44672</v>
@@ -19773,7 +19865,7 @@
         <v>44702</v>
       </c>
       <c r="I22" s="273" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J22" s="275">
         <v>44775</v>
@@ -19797,16 +19889,16 @@
       </c>
       <c r="B23" s="511"/>
       <c r="C23" s="531" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D23" s="500" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E23" s="500" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F23" s="500" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G23" s="437">
         <v>44672</v>
@@ -19815,7 +19907,7 @@
         <v>44702</v>
       </c>
       <c r="I23" s="459" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J23" s="415">
         <v>44772</v>
@@ -19859,7 +19951,7 @@
         <v>44699</v>
       </c>
       <c r="I24" s="540" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J24" s="278">
         <v>44772</v>
@@ -19888,7 +19980,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A25" s="508" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B25" s="524"/>
       <c r="C25" s="501" t="s">
@@ -19898,10 +19990,10 @@
         <v>95</v>
       </c>
       <c r="E25" s="501" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F25" s="501" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G25" s="460"/>
       <c r="H25" s="460"/>
@@ -19922,7 +20014,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C26" s="502" t="s">
         <v>99</v>
@@ -19943,7 +20035,7 @@
         <v>44703</v>
       </c>
       <c r="I26" s="445" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J26" s="279">
         <v>44765</v>
@@ -19994,7 +20086,7 @@
         <v>44700</v>
       </c>
       <c r="I27" s="445" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J27" s="279">
         <v>44763</v>
@@ -20030,13 +20122,13 @@
         <v>106</v>
       </c>
       <c r="D28" s="502" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E28" s="502" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F28" s="502" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G28" s="443">
         <v>44668</v>
@@ -20045,7 +20137,7 @@
         <v>44701</v>
       </c>
       <c r="I28" s="445" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J28" s="279">
         <v>44764</v>
@@ -20096,7 +20188,7 @@
         <v>44704</v>
       </c>
       <c r="I29" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J29" s="282">
         <v>44769</v>
@@ -20138,7 +20230,7 @@
         <v>44706</v>
       </c>
       <c r="I30" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J30" s="279">
         <v>44762</v>
@@ -20180,7 +20272,7 @@
         <v>44700</v>
       </c>
       <c r="I31" s="445" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J31" s="279">
         <v>44769</v>
@@ -20231,7 +20323,7 @@
         <v>44698</v>
       </c>
       <c r="I32" s="465" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J32" s="279">
         <v>44772</v>
@@ -20264,7 +20356,7 @@
         <v>129</v>
       </c>
       <c r="F33" s="503" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G33" s="110">
         <v>44674</v>
@@ -20273,7 +20365,7 @@
         <v>44706</v>
       </c>
       <c r="I33" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J33" s="279">
         <v>44767</v>
@@ -20315,7 +20407,7 @@
         <v>44698</v>
       </c>
       <c r="I34" s="445" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J34" s="279">
         <v>44769</v>
@@ -20366,7 +20458,7 @@
         <v>44698</v>
       </c>
       <c r="I35" s="176" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J35" s="279">
         <v>44762</v>
@@ -20390,16 +20482,16 @@
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="502" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D36" s="502" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E36" s="502" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F36" s="502" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G36" s="443">
         <v>44675</v>
@@ -20408,7 +20500,7 @@
         <v>44709</v>
       </c>
       <c r="I36" s="445" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J36" s="279">
         <v>44766</v>
@@ -20441,16 +20533,16 @@
       </c>
       <c r="B37" s="512"/>
       <c r="C37" s="504" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D37" s="504" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E37" s="536" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F37" s="504" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G37" s="118">
         <v>44667</v>
@@ -20459,7 +20551,7 @@
         <v>44703</v>
       </c>
       <c r="I37" s="183" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J37" s="281">
         <v>44765</v>
@@ -20482,19 +20574,19 @@
         <v>31</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C38" s="458" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D38" s="401" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E38" s="414" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F38" s="401" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G38" s="25">
         <v>44666</v>
@@ -20503,7 +20595,7 @@
         <v>44699</v>
       </c>
       <c r="I38" s="26" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J38" s="278">
         <v>44776</v>
@@ -20529,16 +20621,16 @@
         <v>85</v>
       </c>
       <c r="C39" s="506" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D39" s="503" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E39" s="413" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F39" s="503" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G39" s="27">
         <v>44665</v>
@@ -20547,7 +20639,7 @@
         <v>44700</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J39" s="283">
         <v>44767</v>
@@ -20570,19 +20662,19 @@
         <v>33</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C40" s="505" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D40" s="505" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E40" s="505" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F40" s="505" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G40" s="451">
         <v>44663</v>
@@ -20591,7 +20683,7 @@
         <v>44694</v>
       </c>
       <c r="I40" s="452" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J40" s="522">
         <v>44765</v>
@@ -20624,16 +20716,16 @@
       </c>
       <c r="B41" s="514"/>
       <c r="C41" s="506" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D41" s="506" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E41" s="506" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F41" s="412" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G41" s="62">
         <v>44669</v>
@@ -20642,7 +20734,7 @@
         <v>44699</v>
       </c>
       <c r="I41" s="63" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J41" s="275">
         <v>44762</v>
@@ -20665,19 +20757,19 @@
         <v>35</v>
       </c>
       <c r="B42" s="514" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C42" s="503" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D42" s="503" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E42" s="503" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F42" s="503" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G42" s="19">
         <v>44670</v>
@@ -20686,7 +20778,7 @@
         <v>44700</v>
       </c>
       <c r="I42" s="63" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J42" s="275">
         <v>44768</v>
@@ -20710,16 +20802,16 @@
       </c>
       <c r="B43" s="514"/>
       <c r="C43" s="503" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D43" s="503" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E43" s="503" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F43" s="506" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G43" s="19">
         <v>44672</v>
@@ -20728,7 +20820,7 @@
         <v>44710</v>
       </c>
       <c r="I43" s="63" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J43" s="275">
         <v>44768</v>
@@ -20752,16 +20844,16 @@
       </c>
       <c r="B44" s="515"/>
       <c r="C44" s="503" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D44" s="503" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E44" s="503" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F44" s="503" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G44" s="19">
         <v>44669</v>
@@ -20770,7 +20862,7 @@
         <v>44699</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J44" s="275">
         <v>44768</v>
@@ -20794,16 +20886,16 @@
       </c>
       <c r="B45" s="514"/>
       <c r="C45" s="503" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D45" s="503" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E45" s="503" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F45" s="503" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G45" s="19">
         <v>44670</v>
@@ -20812,7 +20904,7 @@
         <v>44699</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J45" s="275">
         <v>44766</v>
@@ -20836,16 +20928,16 @@
       </c>
       <c r="B46" s="514"/>
       <c r="C46" s="502" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D46" s="502" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E46" s="502" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F46" s="502" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G46" s="455">
         <v>44667</v>
@@ -20854,7 +20946,7 @@
         <v>44697</v>
       </c>
       <c r="I46" s="456" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J46" s="275">
         <v>44760</v>
@@ -20905,7 +20997,7 @@
         <v>44696</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J47" s="288">
         <v>44764</v>
@@ -20947,7 +21039,7 @@
         <v>44704</v>
       </c>
       <c r="I48" s="20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J48" s="288">
         <v>44768</v>
@@ -20989,7 +21081,7 @@
         <v>44700</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J49" s="289">
         <v>44769</v>
@@ -21009,38 +21101,44 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A50" s="524" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B50" s="533"/>
       <c r="J50" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O50" s="1"/>
       <c r="P50" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="R50" s="1"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.15">
       <c r="C51" s="534"/>
       <c r="D51" s="523" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J51" s="316" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P51" s="316" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q51" s="316" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="R4:R6"/>
+    <mergeCell ref="P4:P6"/>
+    <mergeCell ref="O4:O6"/>
     <mergeCell ref="S10:S11"/>
     <mergeCell ref="O3:R3"/>
     <mergeCell ref="S3:S6"/>
@@ -21057,12 +21155,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="R4:R6"/>
-    <mergeCell ref="P4:P6"/>
-    <mergeCell ref="O4:O6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21075,30 +21167,30 @@
   <dimension ref="A1:O46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.375" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.5" style="28" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F2" s="2"/>
       <c r="H2" s="6"/>
@@ -21109,22 +21201,22 @@
       <c r="O3" s="12"/>
     </row>
     <row r="4" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="864" t="s">
+      <c r="A4" s="867" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="867" t="s">
+      <c r="B4" s="870" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="870" t="s">
+      <c r="C4" s="873" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="870" t="s">
+      <c r="D4" s="873" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="810" t="s">
+      <c r="E4" s="820" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="871" t="s">
+      <c r="F4" s="874" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="290" t="s">
@@ -21139,40 +21231,40 @@
       <c r="J4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="860" t="s">
-        <v>260</v>
-      </c>
-      <c r="L4" s="859" t="s">
+      <c r="K4" s="863" t="s">
         <v>261</v>
       </c>
-      <c r="M4" s="859" t="s">
+      <c r="L4" s="857" t="s">
+        <v>262</v>
+      </c>
+      <c r="M4" s="857" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="865"/>
-      <c r="B5" s="868"/>
-      <c r="C5" s="811"/>
-      <c r="D5" s="811"/>
-      <c r="E5" s="811"/>
-      <c r="F5" s="872"/>
+      <c r="A5" s="868"/>
+      <c r="B5" s="871"/>
+      <c r="C5" s="821"/>
+      <c r="D5" s="821"/>
+      <c r="E5" s="821"/>
+      <c r="F5" s="875"/>
       <c r="G5" s="291"/>
       <c r="H5" s="291"/>
       <c r="I5" s="291" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="10"/>
-      <c r="K5" s="861"/>
-      <c r="L5" s="863"/>
-      <c r="M5" s="847"/>
+      <c r="K5" s="864"/>
+      <c r="L5" s="866"/>
+      <c r="M5" s="858"/>
     </row>
     <row r="6" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="866"/>
-      <c r="B6" s="869"/>
-      <c r="C6" s="812"/>
-      <c r="D6" s="812"/>
-      <c r="E6" s="812"/>
-      <c r="F6" s="873"/>
+      <c r="A6" s="869"/>
+      <c r="B6" s="872"/>
+      <c r="C6" s="822"/>
+      <c r="D6" s="822"/>
+      <c r="E6" s="822"/>
+      <c r="F6" s="876"/>
       <c r="G6" s="7" t="s">
         <v>23</v>
       </c>
@@ -21185,11 +21277,11 @@
       <c r="J6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="862"/>
+      <c r="K6" s="865"/>
       <c r="L6" s="194" t="s">
-        <v>267</v>
-      </c>
-      <c r="M6" s="848"/>
+        <v>268</v>
+      </c>
+      <c r="M6" s="859"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7" s="150">
@@ -21217,7 +21309,7 @@
         <v>44336</v>
       </c>
       <c r="I7" s="124" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J7" s="274">
         <v>44401</v>
@@ -21228,7 +21320,7 @@
       </c>
       <c r="L7" s="206"/>
       <c r="M7" s="214" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.15">
@@ -21239,16 +21331,16 @@
         <v>32</v>
       </c>
       <c r="C8" s="221" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D8" s="221" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="221" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F8" s="222" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G8" s="72">
         <v>44307</v>
@@ -21257,7 +21349,7 @@
         <v>44341</v>
       </c>
       <c r="I8" s="135" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J8" s="275">
         <v>44405</v>
@@ -21290,10 +21382,10 @@
         <v>44314</v>
       </c>
       <c r="H9" s="76" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I9" s="141" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J9" s="276">
         <v>44399</v>
@@ -21331,7 +21423,7 @@
         <v>44339</v>
       </c>
       <c r="I10" s="145" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J10" s="275">
         <v>44397</v>
@@ -21369,7 +21461,7 @@
         <v>44333</v>
       </c>
       <c r="I11" s="144" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J11" s="275">
         <v>44400</v>
@@ -21405,7 +21497,7 @@
         <v>44336</v>
       </c>
       <c r="I12" s="146" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J12" s="276">
         <v>44401</v>
@@ -21443,7 +21535,7 @@
         <v>44335</v>
       </c>
       <c r="I13" s="145" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J13" s="274">
         <v>44405</v>
@@ -21463,16 +21555,16 @@
         <v>60</v>
       </c>
       <c r="C14" s="239" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D14" s="239" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E14" s="239" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F14" s="240" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G14" s="110">
         <v>44314</v>
@@ -21481,7 +21573,7 @@
         <v>44341</v>
       </c>
       <c r="I14" s="273" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J14" s="275">
         <v>44405</v>
@@ -21505,7 +21597,7 @@
         <v>63</v>
       </c>
       <c r="E15" s="239" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F15" s="240" t="s">
         <v>65</v>
@@ -21517,7 +21609,7 @@
         <v>44331</v>
       </c>
       <c r="I15" s="144" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J15" s="275">
         <v>44405</v>
@@ -21541,7 +21633,7 @@
         <v>68</v>
       </c>
       <c r="E16" s="239" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F16" s="240" t="s">
         <v>70</v>
@@ -21553,7 +21645,7 @@
         <v>44339</v>
       </c>
       <c r="I16" s="144" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J16" s="275">
         <v>44402</v>
@@ -21577,7 +21669,7 @@
         <v>72</v>
       </c>
       <c r="E17" s="239" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F17" s="240" t="s">
         <v>74</v>
@@ -21589,7 +21681,7 @@
         <v>44336</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J17" s="275">
         <v>44404</v>
@@ -21600,7 +21692,7 @@
       </c>
       <c r="L17" s="201"/>
       <c r="M17" s="110" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.15">
@@ -21627,7 +21719,7 @@
         <v>44339</v>
       </c>
       <c r="I18" s="146" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J18" s="275">
         <v>44399</v>
@@ -21653,7 +21745,7 @@
         <v>81</v>
       </c>
       <c r="E19" s="245" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F19" s="246" t="s">
         <v>83</v>
@@ -21665,7 +21757,7 @@
         <v>44336</v>
       </c>
       <c r="I19" s="145" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J19" s="274">
         <v>44399</v>
@@ -21682,7 +21774,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="247" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C20" s="248" t="s">
         <v>86</v>
@@ -21691,7 +21783,7 @@
         <v>87</v>
       </c>
       <c r="E20" s="248" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F20" s="249" t="s">
         <v>89</v>
@@ -21703,7 +21795,7 @@
         <v>44340</v>
       </c>
       <c r="I20" s="146" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J20" s="277">
         <v>44402</v>
@@ -21741,7 +21833,7 @@
         <v>44336</v>
       </c>
       <c r="I21" s="174" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J21" s="278">
         <v>44401</v>
@@ -21779,7 +21871,7 @@
         <v>44333</v>
       </c>
       <c r="I22" s="176" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J22" s="279">
         <v>44401</v>
@@ -21797,7 +21889,7 @@
       </c>
       <c r="B23" s="253"/>
       <c r="C23" s="254" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D23" s="254" t="s">
         <v>100</v>
@@ -21815,7 +21907,7 @@
         <v>44338</v>
       </c>
       <c r="I23" s="176" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J23" s="280">
         <v>44397</v>
@@ -21833,10 +21925,10 @@
       </c>
       <c r="B24" s="253"/>
       <c r="C24" s="254" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D24" s="254" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E24" s="258" t="s">
         <v>104</v>
@@ -21851,7 +21943,7 @@
         <v>44335</v>
       </c>
       <c r="I24" s="176" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J24" s="281">
         <v>44397</v>
@@ -21869,16 +21961,16 @@
       </c>
       <c r="B25" s="253"/>
       <c r="C25" s="254" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D25" s="254" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E25" s="254" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F25" s="256" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G25" s="72">
         <v>44305</v>
@@ -21887,7 +21979,7 @@
         <v>44336</v>
       </c>
       <c r="I25" s="176" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J25" s="279">
         <v>44401</v>
@@ -21905,7 +21997,7 @@
       </c>
       <c r="B26" s="253"/>
       <c r="C26" s="257" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D26" s="257" t="s">
         <v>111</v>
@@ -21923,7 +22015,7 @@
         <v>44339</v>
       </c>
       <c r="I26" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J26" s="282">
         <v>44398</v>
@@ -21941,7 +22033,7 @@
       </c>
       <c r="B27" s="253"/>
       <c r="C27" s="257" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D27" s="257" t="s">
         <v>115</v>
@@ -21959,7 +22051,7 @@
         <v>44345</v>
       </c>
       <c r="I27" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J27" s="279">
         <v>44402</v>
@@ -21977,7 +22069,7 @@
       </c>
       <c r="B28" s="253"/>
       <c r="C28" s="254" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D28" s="254" t="s">
         <v>119</v>
@@ -21995,7 +22087,7 @@
         <v>44336</v>
       </c>
       <c r="I28" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J28" s="279">
         <v>44399</v>
@@ -22013,7 +22105,7 @@
       </c>
       <c r="B29" s="253"/>
       <c r="C29" s="254" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D29" s="254" t="s">
         <v>123</v>
@@ -22031,7 +22123,7 @@
         <v>44337</v>
       </c>
       <c r="I29" s="271" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J29" s="280">
         <v>44401</v>
@@ -22049,7 +22141,7 @@
       </c>
       <c r="B30" s="253"/>
       <c r="C30" s="254" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D30" s="254" t="s">
         <v>128</v>
@@ -22058,7 +22150,7 @@
         <v>129</v>
       </c>
       <c r="F30" s="256" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G30" s="72">
         <v>44309</v>
@@ -22067,7 +22159,7 @@
         <v>44340</v>
       </c>
       <c r="I30" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J30" s="281">
         <v>44400</v>
@@ -22085,7 +22177,7 @@
       </c>
       <c r="B31" s="253"/>
       <c r="C31" s="254" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D31" s="254" t="s">
         <v>132</v>
@@ -22103,7 +22195,7 @@
         <v>44333</v>
       </c>
       <c r="I31" s="176" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J31" s="279">
         <v>44401</v>
@@ -22121,7 +22213,7 @@
       </c>
       <c r="B32" s="253"/>
       <c r="C32" s="254" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D32" s="254" t="s">
         <v>137</v>
@@ -22139,7 +22231,7 @@
         <v>44333</v>
       </c>
       <c r="I32" s="176" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J32" s="280">
         <v>44400</v>
@@ -22157,16 +22249,16 @@
       </c>
       <c r="B33" s="253"/>
       <c r="C33" s="254" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D33" s="254" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E33" s="254" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F33" s="256" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G33" s="72">
         <v>44301</v>
@@ -22175,7 +22267,7 @@
         <v>44334</v>
       </c>
       <c r="I33" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J33" s="279">
         <v>44397</v>
@@ -22193,16 +22285,16 @@
       </c>
       <c r="B34" s="260"/>
       <c r="C34" s="261" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="261" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" s="248" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F34" s="262" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G34" s="76">
         <v>44307</v>
@@ -22211,7 +22303,7 @@
         <v>44337</v>
       </c>
       <c r="I34" s="183" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J34" s="283">
         <v>44396</v>
@@ -22228,19 +22320,19 @@
         <v>29</v>
       </c>
       <c r="B35" s="250" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" s="251" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D35" s="251" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E35" s="251" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F35" s="263" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G35" s="25">
         <v>44299</v>
@@ -22249,7 +22341,7 @@
         <v>44331</v>
       </c>
       <c r="I35" s="26" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J35" s="284">
         <v>44398</v>
@@ -22269,16 +22361,16 @@
         <v>85</v>
       </c>
       <c r="C36" s="261" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D36" s="261" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E36" s="261" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F36" s="264" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G36" s="27">
         <v>44301</v>
@@ -22287,7 +22379,7 @@
         <v>44334</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J36" s="285">
         <v>44401</v>
@@ -22304,19 +22396,19 @@
         <v>31</v>
       </c>
       <c r="B37" s="250" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C37" s="251" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D37" s="251" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37" s="251" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F37" s="252" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G37" s="16">
         <v>44299</v>
@@ -22325,7 +22417,7 @@
         <v>44330</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J37" s="286">
         <v>44395</v>
@@ -22343,16 +22435,16 @@
       </c>
       <c r="B38" s="253"/>
       <c r="C38" s="265" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D38" s="265" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="265" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F38" s="266" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G38" s="62">
         <v>44299</v>
@@ -22361,7 +22453,7 @@
         <v>44331</v>
       </c>
       <c r="I38" s="63" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J38" s="287">
         <v>44395</v>
@@ -22378,19 +22470,19 @@
         <v>33</v>
       </c>
       <c r="B39" s="253" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C39" s="254" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D39" s="254" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E39" s="254" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F39" s="256" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G39" s="19">
         <v>44305</v>
@@ -22399,7 +22491,7 @@
         <v>44336</v>
       </c>
       <c r="I39" s="63" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J39" s="288">
         <v>44395</v>
@@ -22417,16 +22509,16 @@
       </c>
       <c r="B40" s="253"/>
       <c r="C40" s="254" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D40" s="254" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E40" s="269" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F40" s="270" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G40" s="19">
         <v>44305</v>
@@ -22435,7 +22527,7 @@
         <v>44341</v>
       </c>
       <c r="I40" s="63" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J40" s="288">
         <v>44400</v>
@@ -22453,16 +22545,16 @@
       </c>
       <c r="B41" s="267"/>
       <c r="C41" s="257" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D41" s="257" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E41" s="257" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F41" s="259" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G41" s="19">
         <v>44304</v>
@@ -22471,7 +22563,7 @@
         <v>44337</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J41" s="288">
         <v>44397</v>
@@ -22489,16 +22581,16 @@
       </c>
       <c r="B42" s="253"/>
       <c r="C42" s="254" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D42" s="254" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42" s="268" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F42" s="256" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G42" s="19">
         <v>44305</v>
@@ -22507,7 +22599,7 @@
         <v>44333</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J42" s="288">
         <v>44397</v>
@@ -22525,16 +22617,16 @@
       </c>
       <c r="B43" s="253"/>
       <c r="C43" s="254" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D43" s="254" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" s="254" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F43" s="256" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G43" s="19">
         <v>44301</v>
@@ -22543,7 +22635,7 @@
         <v>44335</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J43" s="288">
         <v>44397</v>
@@ -22561,13 +22653,13 @@
       </c>
       <c r="B44" s="253"/>
       <c r="C44" s="254" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D44" s="254" t="s">
         <v>190</v>
       </c>
       <c r="E44" s="254" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F44" s="256" t="s">
         <v>192</v>
@@ -22579,7 +22671,7 @@
         <v>44331</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="J44" s="288">
         <v>44397</v>
@@ -22597,7 +22689,7 @@
       </c>
       <c r="B45" s="253"/>
       <c r="C45" s="254" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D45" s="254" t="s">
         <v>194</v>
@@ -22615,7 +22707,7 @@
         <v>44340</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J45" s="288">
         <v>44397</v>
@@ -22651,7 +22743,7 @@
         <v>44336</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J46" s="289">
         <v>44397</v>
@@ -22697,27 +22789,27 @@
   <dimension ref="A1:O46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" style="28" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F2" s="2"/>
       <c r="H2" s="6"/>
@@ -22728,22 +22820,22 @@
       <c r="O3" s="12"/>
     </row>
     <row r="4" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="864" t="s">
+      <c r="A4" s="867" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="867" t="s">
+      <c r="B4" s="870" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="870" t="s">
+      <c r="C4" s="873" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="870" t="s">
+      <c r="D4" s="873" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="810" t="s">
+      <c r="E4" s="820" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="871" t="s">
+      <c r="F4" s="874" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="290" t="s">
@@ -22758,36 +22850,36 @@
       <c r="J4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="860" t="s">
-        <v>260</v>
-      </c>
-      <c r="L4" s="859" t="s">
+      <c r="K4" s="863" t="s">
         <v>261</v>
       </c>
+      <c r="L4" s="857" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="865"/>
-      <c r="B5" s="868"/>
-      <c r="C5" s="811"/>
-      <c r="D5" s="811"/>
-      <c r="E5" s="811"/>
-      <c r="F5" s="872"/>
+      <c r="A5" s="868"/>
+      <c r="B5" s="871"/>
+      <c r="C5" s="821"/>
+      <c r="D5" s="821"/>
+      <c r="E5" s="821"/>
+      <c r="F5" s="875"/>
       <c r="G5" s="291"/>
       <c r="H5" s="291"/>
       <c r="I5" s="291" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="10"/>
-      <c r="K5" s="861"/>
-      <c r="L5" s="863"/>
+      <c r="K5" s="864"/>
+      <c r="L5" s="866"/>
     </row>
     <row r="6" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="866"/>
-      <c r="B6" s="869"/>
-      <c r="C6" s="812"/>
-      <c r="D6" s="812"/>
-      <c r="E6" s="812"/>
-      <c r="F6" s="873"/>
+      <c r="A6" s="869"/>
+      <c r="B6" s="872"/>
+      <c r="C6" s="822"/>
+      <c r="D6" s="822"/>
+      <c r="E6" s="822"/>
+      <c r="F6" s="876"/>
       <c r="G6" s="7" t="s">
         <v>23</v>
       </c>
@@ -22800,9 +22892,9 @@
       <c r="J6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="862"/>
+      <c r="K6" s="865"/>
       <c r="L6" s="194" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.15">
@@ -22842,16 +22934,16 @@
         <v>32</v>
       </c>
       <c r="C8" s="131" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D8" s="131" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="131" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F8" s="134" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G8" s="72"/>
       <c r="H8" s="72"/>
@@ -23012,16 +23104,16 @@
         <v>60</v>
       </c>
       <c r="C14" s="106" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D14" s="106" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F14" s="109" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G14" s="110"/>
       <c r="H14" s="72"/>
@@ -23045,7 +23137,7 @@
         <v>63</v>
       </c>
       <c r="E15" s="106" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F15" s="109" t="s">
         <v>65</v>
@@ -23072,7 +23164,7 @@
         <v>68</v>
       </c>
       <c r="E16" s="106" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F16" s="109" t="s">
         <v>70</v>
@@ -23099,7 +23191,7 @@
         <v>72</v>
       </c>
       <c r="E17" s="106" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F17" s="109" t="s">
         <v>74</v>
@@ -23155,7 +23247,7 @@
         <v>81</v>
       </c>
       <c r="E19" s="84" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F19" s="87" t="s">
         <v>83</v>
@@ -23175,7 +23267,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="91" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C20" s="92" t="s">
         <v>86</v>
@@ -23184,7 +23276,7 @@
         <v>87</v>
       </c>
       <c r="E20" s="92" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F20" s="95" t="s">
         <v>89</v>
@@ -23263,7 +23355,7 @@
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D23" s="43" t="s">
         <v>100</v>
@@ -23290,10 +23382,10 @@
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E24" s="73" t="s">
         <v>104</v>
@@ -23317,16 +23409,16 @@
       </c>
       <c r="B25" s="42"/>
       <c r="C25" s="43" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F25" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G25" s="72"/>
       <c r="H25" s="72"/>
@@ -23344,7 +23436,7 @@
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="211" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D26" s="211" t="s">
         <v>111</v>
@@ -23371,7 +23463,7 @@
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="211" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D27" s="211" t="s">
         <v>115</v>
@@ -23398,7 +23490,7 @@
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="43" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D28" s="43" t="s">
         <v>119</v>
@@ -23425,13 +23517,13 @@
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D29" s="43" t="s">
         <v>123</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F29" s="45" t="s">
         <v>125</v>
@@ -23452,7 +23544,7 @@
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="43" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D30" s="43" t="s">
         <v>128</v>
@@ -23461,7 +23553,7 @@
         <v>129</v>
       </c>
       <c r="F30" s="45" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G30" s="72"/>
       <c r="H30" s="72"/>
@@ -23479,7 +23571,7 @@
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="43" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D31" s="43" t="s">
         <v>132</v>
@@ -23506,16 +23598,16 @@
       </c>
       <c r="B32" s="42"/>
       <c r="C32" s="43" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D32" s="43" t="s">
         <v>137</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F32" s="45" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G32" s="72"/>
       <c r="H32" s="72"/>
@@ -23533,16 +23625,16 @@
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E33" s="43" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F33" s="45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G33" s="72"/>
       <c r="H33" s="72"/>
@@ -23560,16 +23652,16 @@
       </c>
       <c r="B34" s="37"/>
       <c r="C34" s="38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" s="92" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F34" s="75" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G34" s="76"/>
       <c r="H34" s="76"/>
@@ -23586,19 +23678,19 @@
         <v>29</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G35" s="25"/>
       <c r="H35" s="25"/>
@@ -23618,16 +23710,16 @@
         <v>85</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G36" s="27"/>
       <c r="H36" s="27"/>
@@ -23644,19 +23736,19 @@
         <v>31</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D37" s="35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F37" s="79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
@@ -23674,16 +23766,16 @@
       </c>
       <c r="B38" s="42"/>
       <c r="C38" s="209" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D38" s="209" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="209" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F38" s="210" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G38" s="62"/>
       <c r="H38" s="62"/>
@@ -23700,19 +23792,19 @@
         <v>33</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E39" s="43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F39" s="45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G39" s="19"/>
       <c r="H39" s="19"/>
@@ -23730,16 +23822,16 @@
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E40" s="43" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F40" s="45" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
@@ -23757,16 +23849,16 @@
       </c>
       <c r="B41" s="48"/>
       <c r="C41" s="211" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D41" s="211" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E41" s="211" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F41" s="212" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G41" s="19"/>
       <c r="H41" s="19"/>
@@ -23784,16 +23876,16 @@
       </c>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42" s="49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F42" s="45" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G42" s="19"/>
       <c r="H42" s="19"/>
@@ -23811,16 +23903,16 @@
       </c>
       <c r="B43" s="42"/>
       <c r="C43" s="43" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" s="43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F43" s="45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G43" s="19"/>
       <c r="H43" s="19"/>
@@ -23838,13 +23930,13 @@
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D44" s="43" t="s">
         <v>190</v>
       </c>
       <c r="E44" s="43" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F44" s="45" t="s">
         <v>192</v>
@@ -23865,7 +23957,7 @@
       </c>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D45" s="43" t="s">
         <v>194</v>
@@ -23936,68 +24028,68 @@
   <dimension ref="A1:S46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="44.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.375" style="28" customWidth="1"/>
-    <col min="15" max="15" width="35.625" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5" style="28" customWidth="1"/>
+    <col min="15" max="15" width="35.5" style="28" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H2" s="2"/>
       <c r="J2" s="6"/>
     </row>
     <row r="3" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="78" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L3" s="2"/>
       <c r="S3" s="12"/>
     </row>
     <row r="4" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="864" t="s">
+      <c r="A4" s="867" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="867" t="s">
+      <c r="B4" s="870" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="870" t="s">
+      <c r="C4" s="873" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="870" t="s">
+      <c r="D4" s="873" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="810" t="s">
-        <v>344</v>
-      </c>
-      <c r="F4" s="810" t="s">
+      <c r="E4" s="820" t="s">
+        <v>345</v>
+      </c>
+      <c r="F4" s="820" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="870" t="s">
-        <v>345</v>
-      </c>
-      <c r="H4" s="871" t="s">
+      <c r="G4" s="873" t="s">
+        <v>346</v>
+      </c>
+      <c r="H4" s="874" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="290" t="s">
@@ -24012,42 +24104,42 @@
       <c r="L4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="876" t="s">
-        <v>346</v>
-      </c>
-      <c r="N4" s="874" t="s">
-        <v>261</v>
+      <c r="M4" s="879" t="s">
+        <v>347</v>
+      </c>
+      <c r="N4" s="877" t="s">
+        <v>262</v>
       </c>
       <c r="O4" s="30"/>
     </row>
     <row r="5" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="865"/>
-      <c r="B5" s="868"/>
-      <c r="C5" s="811"/>
-      <c r="D5" s="811"/>
-      <c r="E5" s="879"/>
-      <c r="F5" s="811"/>
-      <c r="G5" s="811"/>
-      <c r="H5" s="872"/>
+      <c r="A5" s="868"/>
+      <c r="B5" s="871"/>
+      <c r="C5" s="821"/>
+      <c r="D5" s="821"/>
+      <c r="E5" s="882"/>
+      <c r="F5" s="821"/>
+      <c r="G5" s="821"/>
+      <c r="H5" s="875"/>
       <c r="I5" s="291"/>
       <c r="J5" s="291"/>
       <c r="K5" s="291" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="10"/>
-      <c r="M5" s="877"/>
-      <c r="N5" s="875"/>
+      <c r="M5" s="880"/>
+      <c r="N5" s="878"/>
       <c r="O5" s="31"/>
     </row>
     <row r="6" spans="1:19" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="866"/>
-      <c r="B6" s="869"/>
-      <c r="C6" s="812"/>
-      <c r="D6" s="812"/>
-      <c r="E6" s="880"/>
-      <c r="F6" s="812"/>
-      <c r="G6" s="812"/>
-      <c r="H6" s="873"/>
+      <c r="A6" s="869"/>
+      <c r="B6" s="872"/>
+      <c r="C6" s="822"/>
+      <c r="D6" s="822"/>
+      <c r="E6" s="883"/>
+      <c r="F6" s="822"/>
+      <c r="G6" s="822"/>
+      <c r="H6" s="876"/>
       <c r="I6" s="7" t="s">
         <v>23</v>
       </c>
@@ -24060,9 +24152,9 @@
       <c r="L6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="878"/>
+      <c r="M6" s="881"/>
       <c r="N6" s="29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O6" s="32"/>
     </row>
@@ -24080,13 +24172,13 @@
         <v>28</v>
       </c>
       <c r="E7" s="121" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F7" s="120" t="s">
         <v>29</v>
       </c>
       <c r="G7" s="122" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H7" s="123" t="s">
         <v>30</v>
@@ -24118,22 +24210,22 @@
         <v>32</v>
       </c>
       <c r="C8" s="131" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D8" s="131" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="132" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G8" s="133" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H8" s="134" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I8" s="72">
         <v>43575</v>
@@ -24142,7 +24234,7 @@
         <v>43610</v>
       </c>
       <c r="K8" s="135" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L8" s="147">
         <v>43681</v>
@@ -24166,13 +24258,13 @@
         <v>38</v>
       </c>
       <c r="E9" s="138" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F9" s="137" t="s">
         <v>39</v>
       </c>
       <c r="G9" s="139" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H9" s="140" t="s">
         <v>40</v>
@@ -24184,7 +24276,7 @@
         <v>43610</v>
       </c>
       <c r="K9" s="141" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L9" s="148">
         <v>43673</v>
@@ -24210,16 +24302,16 @@
         <v>43</v>
       </c>
       <c r="E10" s="153" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F10" s="152" t="s">
         <v>44</v>
       </c>
       <c r="G10" s="154" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H10" s="155" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I10" s="156">
         <v>43575</v>
@@ -24254,16 +24346,16 @@
         <v>48</v>
       </c>
       <c r="E11" s="160" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F11" s="159" t="s">
         <v>49</v>
       </c>
       <c r="G11" s="161" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H11" s="162" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I11" s="163">
         <v>43577</v>
@@ -24296,16 +24388,16 @@
         <v>52</v>
       </c>
       <c r="E12" s="167" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F12" s="166" t="s">
         <v>53</v>
       </c>
       <c r="G12" s="168" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H12" s="169" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I12" s="170">
         <v>43578</v>
@@ -24340,16 +24432,16 @@
         <v>57</v>
       </c>
       <c r="E13" s="100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F13" s="99" t="s">
         <v>58</v>
       </c>
       <c r="G13" s="101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H13" s="102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I13" s="103">
         <v>43572</v>
@@ -24358,7 +24450,7 @@
         <v>43602</v>
       </c>
       <c r="K13" s="145" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L13" s="24">
         <v>43674</v>
@@ -24368,7 +24460,7 @@
       </c>
       <c r="N13" s="54"/>
       <c r="O13" s="129" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.15">
@@ -24379,22 +24471,22 @@
         <v>60</v>
       </c>
       <c r="C14" s="106" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D14" s="106" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E14" s="107" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F14" s="106" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G14" s="108" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H14" s="109" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I14" s="110">
         <v>43577</v>
@@ -24403,10 +24495,10 @@
         <v>43610</v>
       </c>
       <c r="K14" s="144" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L14" s="147" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M14" s="186"/>
       <c r="N14" s="52"/>
@@ -24424,16 +24516,16 @@
         <v>63</v>
       </c>
       <c r="E15" s="107" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F15" s="111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G15" s="108" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H15" s="109" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I15" s="110">
         <v>43569</v>
@@ -24445,7 +24537,7 @@
         <v>46</v>
       </c>
       <c r="L15" s="147" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M15" s="186"/>
       <c r="N15" s="52"/>
@@ -24460,19 +24552,19 @@
         <v>67</v>
       </c>
       <c r="D16" s="106" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E16" s="107" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F16" s="106" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G16" s="108" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H16" s="109" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I16" s="110">
         <v>43571</v>
@@ -24481,7 +24573,7 @@
         <v>43608</v>
       </c>
       <c r="K16" s="144" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L16" s="147">
         <v>43674</v>
@@ -24491,7 +24583,7 @@
       </c>
       <c r="N16" s="52"/>
       <c r="O16" s="129" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.15">
@@ -24506,16 +24598,16 @@
         <v>72</v>
       </c>
       <c r="E17" s="107" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F17" s="106" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G17" s="108" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H17" s="109" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I17" s="110">
         <v>43574</v>
@@ -24527,7 +24619,7 @@
         <v>46</v>
       </c>
       <c r="L17" s="147" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M17" s="186"/>
       <c r="N17" s="52"/>
@@ -24545,13 +24637,13 @@
         <v>76</v>
       </c>
       <c r="E18" s="115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F18" s="114" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="116" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H18" s="117" t="s">
         <v>78</v>
@@ -24566,7 +24658,7 @@
         <v>46</v>
       </c>
       <c r="L18" s="147" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M18" s="27"/>
       <c r="N18" s="55"/>
@@ -24586,13 +24678,13 @@
         <v>81</v>
       </c>
       <c r="E19" s="85" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F19" s="84" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G19" s="86" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H19" s="87" t="s">
         <v>83</v>
@@ -24604,7 +24696,7 @@
         <v>43607</v>
       </c>
       <c r="K19" s="145" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L19" s="24">
         <v>43670</v>
@@ -24615,7 +24707,7 @@
       <c r="N19" s="54"/>
       <c r="O19" s="77"/>
       <c r="P19" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -24623,25 +24715,25 @@
         <v>14</v>
       </c>
       <c r="B20" s="91" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C20" s="92" t="s">
         <v>86</v>
       </c>
       <c r="D20" s="92" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E20" s="93" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F20" s="92" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G20" s="94" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H20" s="95" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I20" s="96">
         <v>43571</v>
@@ -24650,7 +24742,7 @@
         <v>43607</v>
       </c>
       <c r="K20" s="146" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L20" s="148">
         <v>43676</v>
@@ -24660,10 +24752,10 @@
       </c>
       <c r="N20" s="55"/>
       <c r="O20" s="77" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.15">
@@ -24677,19 +24769,19 @@
         <v>91</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F21" s="35" t="s">
         <v>93</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H21" s="79" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I21" s="80">
         <v>43575</v>
@@ -24698,7 +24790,7 @@
         <v>43605</v>
       </c>
       <c r="K21" s="174" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L21" s="175">
         <v>43678</v>
@@ -24709,10 +24801,10 @@
       </c>
       <c r="N21" s="54"/>
       <c r="O21" s="142" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -24729,16 +24821,16 @@
         <v>95</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F22" s="81" t="s">
         <v>96</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H22" s="45" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I22" s="72">
         <v>43574</v>
@@ -24747,7 +24839,7 @@
         <v>43602</v>
       </c>
       <c r="K22" s="176" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L22" s="177">
         <v>43676</v>
@@ -24758,10 +24850,10 @@
       </c>
       <c r="N22" s="52"/>
       <c r="O22" s="143" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.15">
@@ -24770,22 +24862,22 @@
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D23" s="43" t="s">
         <v>100</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F23" s="56" t="s">
         <v>101</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H23" s="45" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I23" s="72">
         <v>43574</v>
@@ -24794,7 +24886,7 @@
         <v>43605</v>
       </c>
       <c r="K23" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L23" s="178">
         <v>43667</v>
@@ -24805,10 +24897,10 @@
       </c>
       <c r="N23" s="52"/>
       <c r="O23" s="143" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -24817,22 +24909,22 @@
       </c>
       <c r="B24" s="42"/>
       <c r="C24" s="43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F24" s="73" t="s">
         <v>104</v>
       </c>
       <c r="G24" s="44" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H24" s="45" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I24" s="72">
         <v>43574</v>
@@ -24841,7 +24933,7 @@
         <v>43602</v>
       </c>
       <c r="K24" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L24" s="179">
         <v>43665</v>
@@ -24852,10 +24944,10 @@
       </c>
       <c r="N24" s="52"/>
       <c r="O24" s="143" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -24864,22 +24956,22 @@
       </c>
       <c r="B25" s="42"/>
       <c r="C25" s="43" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H25" s="45" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I25" s="72">
         <v>43573</v>
@@ -24888,7 +24980,7 @@
         <v>43604</v>
       </c>
       <c r="K25" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L25" s="180">
         <v>43671</v>
@@ -24899,10 +24991,10 @@
       </c>
       <c r="N25" s="52"/>
       <c r="O25" s="143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.15">
@@ -24911,22 +25003,22 @@
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="43" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D26" s="43" t="s">
         <v>111</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F26" s="43" t="s">
         <v>216</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I26" s="72">
         <v>43574</v>
@@ -24935,16 +25027,16 @@
         <v>43605</v>
       </c>
       <c r="K26" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L26" s="181"/>
       <c r="M26" s="193"/>
       <c r="N26" s="52"/>
       <c r="O26" s="143" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.15">
@@ -24953,22 +25045,22 @@
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="43" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D27" s="43" t="s">
         <v>115</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F27" s="56" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H27" s="45" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I27" s="72">
         <v>43575</v>
@@ -24977,7 +25069,7 @@
         <v>43611</v>
       </c>
       <c r="K27" s="176" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L27" s="182">
         <v>43672</v>
@@ -24989,7 +25081,7 @@
       <c r="N27" s="52"/>
       <c r="O27" s="143"/>
       <c r="P27" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.15">
@@ -24998,22 +25090,22 @@
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="43" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D28" s="43" t="s">
         <v>119</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F28" s="43" t="s">
         <v>120</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H28" s="45" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I28" s="72">
         <v>43570</v>
@@ -25022,7 +25114,7 @@
         <v>43602</v>
       </c>
       <c r="K28" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L28" s="182">
         <v>43673</v>
@@ -25034,7 +25126,7 @@
       <c r="N28" s="52"/>
       <c r="O28" s="143"/>
       <c r="P28" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.15">
@@ -25043,22 +25135,22 @@
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D29" s="43" t="s">
         <v>123</v>
       </c>
       <c r="E29" s="41" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G29" s="44" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H29" s="45" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I29" s="72">
         <v>43575</v>
@@ -25067,7 +25159,7 @@
         <v>43603</v>
       </c>
       <c r="K29" s="176" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L29" s="178">
         <v>43668</v>
@@ -25078,7 +25170,7 @@
       </c>
       <c r="N29" s="52"/>
       <c r="O29" s="143" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
@@ -25087,22 +25179,22 @@
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="43" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D30" s="43" t="s">
         <v>128</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F30" s="43" t="s">
         <v>129</v>
       </c>
       <c r="G30" s="44" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H30" s="45" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I30" s="72">
         <v>43578</v>
@@ -25111,7 +25203,7 @@
         <v>43610</v>
       </c>
       <c r="K30" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L30" s="179">
         <v>43668</v>
@@ -25129,22 +25221,22 @@
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="43" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D31" s="43" t="s">
         <v>132</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F31" s="43" t="s">
         <v>218</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H31" s="45" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I31" s="72">
         <v>43572</v>
@@ -25153,7 +25245,7 @@
         <v>43602</v>
       </c>
       <c r="K31" s="176" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L31" s="180">
         <v>43678</v>
@@ -25164,7 +25256,7 @@
       </c>
       <c r="N31" s="52"/>
       <c r="O31" s="143" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.15">
@@ -25173,22 +25265,22 @@
       </c>
       <c r="B32" s="42"/>
       <c r="C32" s="43" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D32" s="43" t="s">
         <v>137</v>
       </c>
       <c r="E32" s="41" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G32" s="44" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H32" s="45" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I32" s="72">
         <v>43578</v>
@@ -25197,7 +25289,7 @@
         <v>43608</v>
       </c>
       <c r="K32" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L32" s="178">
         <v>43671</v>
@@ -25208,7 +25300,7 @@
       </c>
       <c r="N32" s="52"/>
       <c r="O32" s="143" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.15">
@@ -25217,22 +25309,22 @@
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E33" s="41" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H33" s="45" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I33" s="72">
         <v>43578</v>
@@ -25241,7 +25333,7 @@
         <v>43608</v>
       </c>
       <c r="K33" s="176" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L33" s="182">
         <v>43670</v>
@@ -25252,7 +25344,7 @@
       </c>
       <c r="N33" s="52"/>
       <c r="O33" s="143" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.15">
@@ -25261,22 +25353,22 @@
       </c>
       <c r="B34" s="37"/>
       <c r="C34" s="38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E34" s="39" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F34" s="57" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G34" s="40" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H34" s="75" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I34" s="76">
         <v>43571</v>
@@ -25285,7 +25377,7 @@
         <v>43605</v>
       </c>
       <c r="K34" s="183" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L34" s="184">
         <v>43670</v>
@@ -25296,7 +25388,7 @@
       </c>
       <c r="N34" s="55"/>
       <c r="O34" s="143" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.15">
@@ -25304,23 +25396,23 @@
         <v>29</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E35" s="35"/>
       <c r="F35" s="35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G35" s="46" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H35" s="36" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I35" s="25">
         <v>43569</v>
@@ -25329,7 +25421,7 @@
         <v>43602</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L35" s="13">
         <v>43666</v>
@@ -25349,20 +25441,20 @@
         <v>85</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" s="38"/>
       <c r="F36" s="38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G36" s="47" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H36" s="40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I36" s="27">
         <v>43571</v>
@@ -25371,7 +25463,7 @@
         <v>43604</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L36" s="15">
         <v>43673</v>
@@ -25388,25 +25480,25 @@
         <v>31</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D37" s="35" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E37" s="128" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G37" s="36" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H37" s="79" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I37" s="16">
         <v>43568</v>
@@ -25415,7 +25507,7 @@
         <v>43598</v>
       </c>
       <c r="K37" s="17" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L37" s="18">
         <v>43666</v>
@@ -25433,22 +25525,22 @@
       </c>
       <c r="B38" s="42"/>
       <c r="C38" s="58" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D38" s="58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="59" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F38" s="58" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G38" s="60" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H38" s="61" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I38" s="62">
         <v>43565</v>
@@ -25457,7 +25549,7 @@
         <v>43598</v>
       </c>
       <c r="K38" s="63" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L38" s="64">
         <v>43657</v>
@@ -25474,25 +25566,25 @@
         <v>33</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C39" s="43" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F39" s="43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G39" s="44" t="s">
+        <v>449</v>
+      </c>
+      <c r="H39" s="45" t="s">
         <v>448</v>
-      </c>
-      <c r="H39" s="45" t="s">
-        <v>447</v>
       </c>
       <c r="I39" s="19">
         <v>43573</v>
@@ -25501,7 +25593,7 @@
         <v>43607</v>
       </c>
       <c r="K39" s="20" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L39" s="21">
         <v>43663</v>
@@ -25519,22 +25611,22 @@
       </c>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E40" s="41" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F40" s="43" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G40" s="44" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H40" s="45" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I40" s="19">
         <v>43573</v>
@@ -25543,7 +25635,7 @@
         <v>43603</v>
       </c>
       <c r="K40" s="20" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L40" s="21">
         <v>43664</v>
@@ -25561,22 +25653,22 @@
       </c>
       <c r="B41" s="48"/>
       <c r="C41" s="56" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F41" s="56" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G41" s="65" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H41" s="66" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I41" s="19">
         <v>43573</v>
@@ -25585,7 +25677,7 @@
         <v>43604</v>
       </c>
       <c r="K41" s="20" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L41" s="21">
         <v>43669</v>
@@ -25602,22 +25694,22 @@
       </c>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42" s="41" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F42" s="49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G42" s="50" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H42" s="45" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I42" s="19">
         <v>43576</v>
@@ -25626,7 +25718,7 @@
         <v>43602</v>
       </c>
       <c r="K42" s="20" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L42" s="21">
         <v>43666</v>
@@ -25643,22 +25735,22 @@
       </c>
       <c r="B43" s="42"/>
       <c r="C43" s="43" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" s="41" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F43" s="43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G43" s="44" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H43" s="45" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I43" s="19">
         <v>43573</v>
@@ -25667,7 +25759,7 @@
         <v>43602</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L43" s="21">
         <v>43670</v>
@@ -25684,22 +25776,22 @@
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D44" s="43" t="s">
         <v>190</v>
       </c>
       <c r="E44" s="41" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F44" s="43" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G44" s="44" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H44" s="45" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I44" s="19">
         <v>43570</v>
@@ -25708,7 +25800,7 @@
         <v>43602</v>
       </c>
       <c r="K44" s="20" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L44" s="21">
         <v>43664</v>
@@ -25725,22 +25817,22 @@
       </c>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D45" s="43" t="s">
         <v>194</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F45" s="43" t="s">
         <v>195</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H45" s="45" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I45" s="19">
         <v>43577</v>
@@ -25772,16 +25864,16 @@
         <v>198</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F46" s="57" t="s">
         <v>199</v>
       </c>
       <c r="G46" s="68" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H46" s="69" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I46" s="22">
         <v>43574</v>
@@ -25790,7 +25882,7 @@
         <v>43604</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="L46" s="23">
         <v>43668</v>
@@ -25822,6 +25914,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <SharedWithUsers xmlns="1bc2cdaf-bec1-4fca-90f0-1089d62d0a15">
@@ -25837,15 +25938,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26090,26 +26182,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77C55F40-6D2C-4A3B-8A4E-5E284031751D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1CF16C-D8DE-4EBF-93E0-AD6D6C4EADE9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="1bc2cdaf-bec1-4fca-90f0-1089d62d0a15"/>
-    <ds:schemaRef ds:uri="eb55df30-2a34-45f7-8c90-b31534229aa7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F1CF16C-D8DE-4EBF-93E0-AD6D6C4EADE9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77C55F40-6D2C-4A3B-8A4E-5E284031751D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1bc2cdaf-bec1-4fca-90f0-1089d62d0a15"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="eb55df30-2a34-45f7-8c90-b31534229aa7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
